--- a/experiments/feature_ablation.xlsx
+++ b/experiments/feature_ablation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BigData\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF48830F-36AF-404F-881B-ED9E632A7B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7389ED2-A495-4418-B6E8-4226E84BDC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3310" yWindow="2210" windowWidth="19200" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="290">
   <si>
     <t>ID</t>
   </si>
@@ -673,10 +673,7 @@
     <t>Bỏ DEPARTURE_DELAY</t>
   </si>
   <si>
-    <t>Nhóm quyết</t>
-  </si>
-  <si>
-    <t>Hòa; nó vẫn được dùng qua phép cộng arrival = DEPARTURE_DELAY + gain</t>
+    <t>Hòa; gain phẳng theo nó (trung vị −6 phút ở mọi mức trễ). Vẫn dùng qua phép cộng arrival = DEPARTURE_DELAY + gain</t>
   </si>
   <si>
     <t>Nguồn</t>
@@ -3252,7 +3249,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" ht="42" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>208</v>
       </c>
@@ -3266,7 +3263,7 @@
         <v>204</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3">
         <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
@@ -3289,7 +3286,7 @@
         <v>2.4819999999999842E-3</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>207</v>
@@ -3322,28 +3319,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -3354,16 +3351,16 @@
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G2" s="4">
         <v>1.8089999999999998E-2</v>
@@ -3384,16 +3381,16 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G3" s="4">
         <v>1.6056000000000001E-2</v>
@@ -3414,16 +3411,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G4" s="4">
         <v>5.4999999999999997E-3</v>
@@ -3444,16 +3441,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G5" s="4">
         <v>0.63741999999999999</v>
@@ -3474,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G6" s="4">
         <v>0.17575099999999999</v>
@@ -3504,16 +3501,16 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G7" s="4">
         <v>0.63796600000000003</v>
@@ -3534,16 +3531,16 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G8" s="4">
         <v>0.16984199999999999</v>
@@ -3564,16 +3561,16 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G9" s="4">
         <v>0.65610599999999997</v>
@@ -3594,16 +3591,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G10" s="4">
         <v>0.18690200000000001</v>
@@ -3624,16 +3621,16 @@
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G11" s="4">
         <v>1.8089999999999998E-2</v>
@@ -3654,16 +3651,16 @@
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G12" s="4">
         <v>1.6056000000000001E-2</v>
@@ -3684,16 +3681,16 @@
         <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G13" s="4">
         <v>5.4999999999999997E-3</v>
@@ -3714,16 +3711,16 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G14" s="4">
         <v>0.63741999999999999</v>
@@ -3744,16 +3741,16 @@
         <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G15" s="4">
         <v>0.17575099999999999</v>
@@ -3774,16 +3771,16 @@
         <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G16" s="4">
         <v>0.63796600000000003</v>
@@ -3804,16 +3801,16 @@
         <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G17" s="4">
         <v>0.16984199999999999</v>
@@ -3834,16 +3831,16 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G18" s="4">
         <v>0.65610599999999997</v>
@@ -3864,16 +3861,16 @@
         <v>26</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G19" s="4">
         <v>0.18690200000000001</v>
@@ -3900,10 +3897,10 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G20" s="4">
         <v>2.5191999999999999E-2</v>
@@ -3930,10 +3927,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G21" s="4">
         <v>5.4732999999999997E-2</v>
@@ -3960,10 +3957,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G22" s="4">
         <v>5.5019999999999999E-2</v>
@@ -3990,10 +3987,10 @@
         <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G23" s="4">
         <v>0.64579699999999995</v>
@@ -4020,10 +4017,10 @@
         <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G24" s="4">
         <v>0.18444099999999999</v>
@@ -4050,10 +4047,10 @@
         <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G25" s="4">
         <v>0.67225000000000001</v>
@@ -4080,10 +4077,10 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G26" s="4">
         <v>0.248747</v>
@@ -4110,10 +4107,10 @@
         <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G27" s="4">
         <v>0.68498099999999995</v>
@@ -4140,10 +4137,10 @@
         <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G28" s="4">
         <v>0.26935999999999999</v>
@@ -4170,10 +4167,10 @@
         <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G29" s="4">
         <v>0.20142399999999999</v>
@@ -4200,10 +4197,10 @@
         <v>37</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G30" s="4">
         <v>0.26522499999999999</v>
@@ -4230,10 +4227,10 @@
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G31" s="4">
         <v>0.25540499999999999</v>
@@ -4260,10 +4257,10 @@
         <v>37</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G32" s="4">
         <v>0.77444199999999996</v>
@@ -4290,10 +4287,10 @@
         <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G33" s="4">
         <v>0.455822</v>
@@ -4320,10 +4317,10 @@
         <v>37</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G34" s="4">
         <v>0.79982699999999995</v>
@@ -4350,10 +4347,10 @@
         <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G35" s="4">
         <v>0.51657500000000001</v>
@@ -4380,10 +4377,10 @@
         <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G36" s="4">
         <v>0.81671899999999997</v>
@@ -4410,10 +4407,10 @@
         <v>37</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G37" s="4">
         <v>0.57144899999999998</v>
@@ -4440,10 +4437,10 @@
         <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G38" s="4">
         <v>0.266625</v>
@@ -4470,10 +4467,10 @@
         <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G39" s="4">
         <v>0.31279600000000002</v>
@@ -4500,10 +4497,10 @@
         <v>43</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G40" s="4">
         <v>0.311164</v>
@@ -4530,10 +4527,10 @@
         <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G41" s="4">
         <v>0.80227199999999999</v>
@@ -4560,10 +4557,10 @@
         <v>43</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G42" s="4">
         <v>0.52499899999999999</v>
@@ -4590,10 +4587,10 @@
         <v>43</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G43" s="4">
         <v>0.83535199999999998</v>
@@ -4620,10 +4617,10 @@
         <v>43</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G44" s="4">
         <v>0.61062700000000003</v>
@@ -4650,10 +4647,10 @@
         <v>43</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G45" s="4">
         <v>0.83543599999999996</v>
@@ -4680,10 +4677,10 @@
         <v>43</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G46" s="4">
         <v>0.62279099999999998</v>
@@ -4710,10 +4707,10 @@
         <v>49</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G47" s="4">
         <v>0.266625</v>
@@ -4740,10 +4737,10 @@
         <v>49</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G48" s="4">
         <v>0.31279600000000002</v>
@@ -4770,10 +4767,10 @@
         <v>49</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G49" s="4">
         <v>0.311164</v>
@@ -4800,10 +4797,10 @@
         <v>49</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G50" s="4">
         <v>0.80227199999999999</v>
@@ -4830,10 +4827,10 @@
         <v>49</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G51" s="4">
         <v>0.52499899999999999</v>
@@ -4860,10 +4857,10 @@
         <v>49</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G52" s="4">
         <v>0.83535199999999998</v>
@@ -4890,10 +4887,10 @@
         <v>49</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G53" s="4">
         <v>0.61062700000000003</v>
@@ -4920,10 +4917,10 @@
         <v>49</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G54" s="4">
         <v>0.83543599999999996</v>
@@ -4950,10 +4947,10 @@
         <v>49</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G55" s="4">
         <v>0.62279099999999998</v>
@@ -4974,16 +4971,16 @@
         <v>54</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G56" s="4">
         <v>1.8089999999999998E-2</v>
@@ -5004,16 +5001,16 @@
         <v>54</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G57" s="4">
         <v>1.6056000000000001E-2</v>
@@ -5034,16 +5031,16 @@
         <v>54</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G58" s="4">
         <v>5.4999999999999997E-3</v>
@@ -5064,16 +5061,16 @@
         <v>54</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G59" s="4">
         <v>0.63741999999999999</v>
@@ -5094,16 +5091,16 @@
         <v>54</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G60" s="4">
         <v>0.17575099999999999</v>
@@ -5124,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G61" s="4">
         <v>0.63796600000000003</v>
@@ -5154,16 +5151,16 @@
         <v>54</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G62" s="4">
         <v>0.16984199999999999</v>
@@ -5184,16 +5181,16 @@
         <v>54</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G63" s="4">
         <v>0.65610599999999997</v>
@@ -5214,16 +5211,16 @@
         <v>54</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G64" s="4">
         <v>0.18690200000000001</v>
@@ -5250,10 +5247,10 @@
         <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G65" s="4">
         <v>2.5191999999999999E-2</v>
@@ -5280,10 +5277,10 @@
         <v>58</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G66" s="4">
         <v>5.4732999999999997E-2</v>
@@ -5310,10 +5307,10 @@
         <v>58</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G67" s="4">
         <v>5.5019999999999999E-2</v>
@@ -5340,10 +5337,10 @@
         <v>58</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G68" s="4">
         <v>0.64579699999999995</v>
@@ -5370,10 +5367,10 @@
         <v>58</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G69" s="4">
         <v>0.18444099999999999</v>
@@ -5400,10 +5397,10 @@
         <v>58</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G70" s="4">
         <v>0.67225000000000001</v>
@@ -5430,10 +5427,10 @@
         <v>58</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G71" s="4">
         <v>0.248747</v>
@@ -5460,10 +5457,10 @@
         <v>58</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G72" s="4">
         <v>0.68498099999999995</v>
@@ -5490,10 +5487,10 @@
         <v>58</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G73" s="4">
         <v>0.26935999999999999</v>
@@ -5520,10 +5517,10 @@
         <v>61</v>
       </c>
       <c r="E74" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G74" s="4">
         <v>0.266625</v>
@@ -5550,10 +5547,10 @@
         <v>61</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G75" s="4">
         <v>0.31279600000000002</v>
@@ -5580,10 +5577,10 @@
         <v>61</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G76" s="4">
         <v>0.311164</v>
@@ -5610,10 +5607,10 @@
         <v>61</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G77" s="4">
         <v>0.80227199999999999</v>
@@ -5640,10 +5637,10 @@
         <v>61</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G78" s="4">
         <v>0.52499899999999999</v>
@@ -5670,10 +5667,10 @@
         <v>61</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G79" s="4">
         <v>0.83535199999999998</v>
@@ -5700,10 +5697,10 @@
         <v>61</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G80" s="4">
         <v>0.61062700000000003</v>
@@ -5730,10 +5727,10 @@
         <v>61</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G81" s="4">
         <v>0.83543599999999996</v>
@@ -5760,10 +5757,10 @@
         <v>61</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G82" s="4">
         <v>0.62279099999999998</v>
@@ -5784,16 +5781,16 @@
         <v>66</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E83" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G83" s="4">
         <v>0.265982</v>
@@ -5814,16 +5811,16 @@
         <v>66</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G84" s="4">
         <v>0.31615300000000002</v>
@@ -5844,16 +5841,16 @@
         <v>66</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G85" s="4">
         <v>0.31152299999999999</v>
@@ -5874,16 +5871,16 @@
         <v>66</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E86" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G86" s="4">
         <v>0.79934400000000005</v>
@@ -5904,16 +5901,16 @@
         <v>66</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G87" s="4">
         <v>0.52996799999999999</v>
@@ -5934,16 +5931,16 @@
         <v>66</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G88" s="4">
         <v>0.82991999999999999</v>
@@ -5964,16 +5961,16 @@
         <v>66</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G89" s="4">
         <v>0.609954</v>
@@ -5994,16 +5991,16 @@
         <v>66</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G90" s="4">
         <v>0.83391700000000002</v>
@@ -6024,16 +6021,16 @@
         <v>66</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G91" s="4">
         <v>0.619668</v>
@@ -6054,16 +6051,16 @@
         <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E92" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G92" s="4">
         <v>0.265982</v>
@@ -6084,16 +6081,16 @@
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G93" s="4">
         <v>0.31615300000000002</v>
@@ -6114,16 +6111,16 @@
         <v>71</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G94" s="4">
         <v>0.31152299999999999</v>
@@ -6144,16 +6141,16 @@
         <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E95" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G95" s="4">
         <v>0.79934400000000005</v>
@@ -6174,16 +6171,16 @@
         <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G96" s="4">
         <v>0.52996799999999999</v>
@@ -6204,16 +6201,16 @@
         <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G97" s="4">
         <v>0.82991999999999999</v>
@@ -6234,16 +6231,16 @@
         <v>71</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G98" s="4">
         <v>0.609954</v>
@@ -6264,16 +6261,16 @@
         <v>71</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G99" s="4">
         <v>0.83391700000000002</v>
@@ -6294,16 +6291,16 @@
         <v>71</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G100" s="4">
         <v>0.619668</v>
@@ -6324,16 +6321,16 @@
         <v>77</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G101" s="4">
         <v>0.265982</v>
@@ -6354,16 +6351,16 @@
         <v>77</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G102" s="4">
         <v>0.31615300000000002</v>
@@ -6384,16 +6381,16 @@
         <v>77</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G103" s="4">
         <v>0.31152299999999999</v>
@@ -6414,16 +6411,16 @@
         <v>77</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E104" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G104" s="4">
         <v>0.79934400000000005</v>
@@ -6444,16 +6441,16 @@
         <v>77</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G105" s="4">
         <v>0.52996799999999999</v>
@@ -6474,16 +6471,16 @@
         <v>77</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G106" s="4">
         <v>0.82991999999999999</v>
@@ -6504,16 +6501,16 @@
         <v>77</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G107" s="4">
         <v>0.609954</v>
@@ -6534,16 +6531,16 @@
         <v>77</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G108" s="4">
         <v>0.83391700000000002</v>
@@ -6564,16 +6561,16 @@
         <v>77</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G109" s="4">
         <v>0.619668</v>
@@ -6597,13 +6594,13 @@
         <v>82</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E110" s="2" t="s">
+      <c r="F110" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G110" s="4">
         <v>1.9293999999999999E-2</v>
@@ -6627,13 +6624,13 @@
         <v>82</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G111" s="4">
         <v>1.8152000000000001E-2</v>
@@ -6657,13 +6654,13 @@
         <v>82</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G112" s="4">
         <v>2.6574E-2</v>
@@ -6687,13 +6684,13 @@
         <v>82</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E113" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G113" s="4">
         <v>0.63682000000000005</v>
@@ -6717,13 +6714,13 @@
         <v>82</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G114" s="4">
         <v>0.17542099999999999</v>
@@ -6747,13 +6744,13 @@
         <v>82</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G115" s="4">
         <v>0.64645300000000006</v>
@@ -6777,13 +6774,13 @@
         <v>82</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G116" s="4">
         <v>0.17816699999999999</v>
@@ -6807,13 +6804,13 @@
         <v>82</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G117" s="4">
         <v>0.66634899999999997</v>
@@ -6837,13 +6834,13 @@
         <v>82</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G118" s="4">
         <v>0.19419500000000001</v>
@@ -6864,16 +6861,16 @@
         <v>88</v>
       </c>
       <c r="C119" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E119" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G119" s="4">
         <v>0.245472</v>
@@ -6894,16 +6891,16 @@
         <v>88</v>
       </c>
       <c r="C120" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D120" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E120" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G120" s="4">
         <v>0.282416</v>
@@ -6924,16 +6921,16 @@
         <v>88</v>
       </c>
       <c r="C121" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E121" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G121" s="4">
         <v>0.28014600000000001</v>
@@ -6954,16 +6951,16 @@
         <v>88</v>
       </c>
       <c r="C122" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E122" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G122" s="4">
         <v>0.80170399999999997</v>
@@ -6984,16 +6981,16 @@
         <v>88</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E123" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G123" s="4">
         <v>0.553122</v>
@@ -7014,16 +7011,16 @@
         <v>88</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E124" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G124" s="4">
         <v>0.82854399999999995</v>
@@ -7044,16 +7041,16 @@
         <v>88</v>
       </c>
       <c r="C125" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E125" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G125" s="4">
         <v>0.61828399999999994</v>
@@ -7074,16 +7071,16 @@
         <v>88</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E126" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G126" s="4">
         <v>0.83161499999999999</v>
@@ -7104,16 +7101,16 @@
         <v>88</v>
       </c>
       <c r="C127" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="E127" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G127" s="4">
         <v>0.63358099999999995</v>
@@ -7134,16 +7131,16 @@
         <v>94</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E128" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G128" s="4">
         <v>0.245472</v>
@@ -7164,16 +7161,16 @@
         <v>94</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G129" s="4">
         <v>0.282416</v>
@@ -7194,16 +7191,16 @@
         <v>94</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G130" s="4">
         <v>0.28014600000000001</v>
@@ -7224,16 +7221,16 @@
         <v>94</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E131" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G131" s="4">
         <v>0.80169299999999999</v>
@@ -7254,16 +7251,16 @@
         <v>94</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G132" s="4">
         <v>0.55311999999999995</v>
@@ -7284,16 +7281,16 @@
         <v>94</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G133" s="4">
         <v>0.82854399999999995</v>
@@ -7314,16 +7311,16 @@
         <v>94</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G134" s="4">
         <v>0.61828399999999994</v>
@@ -7344,16 +7341,16 @@
         <v>94</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G135" s="4">
         <v>0.83161499999999999</v>
@@ -7374,16 +7371,16 @@
         <v>94</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G136" s="4">
         <v>0.63358099999999995</v>
@@ -7404,16 +7401,16 @@
         <v>94</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E137" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G137" s="4">
         <v>0.245472</v>
@@ -7434,16 +7431,16 @@
         <v>94</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G138" s="4">
         <v>0.282416</v>
@@ -7464,16 +7461,16 @@
         <v>94</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G139" s="4">
         <v>0.28014600000000001</v>
@@ -7494,16 +7491,16 @@
         <v>94</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E140" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G140" s="4">
         <v>0.80169299999999999</v>
@@ -7524,16 +7521,16 @@
         <v>94</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G141" s="4">
         <v>0.55311999999999995</v>
@@ -7554,16 +7551,16 @@
         <v>94</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G142" s="4">
         <v>0.82854399999999995</v>
@@ -7584,16 +7581,16 @@
         <v>94</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G143" s="4">
         <v>0.61828399999999994</v>
@@ -7614,16 +7611,16 @@
         <v>94</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G144" s="4">
         <v>0.83161499999999999</v>
@@ -7644,16 +7641,16 @@
         <v>94</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G145" s="4">
         <v>0.63358099999999995</v>
@@ -7674,16 +7671,16 @@
         <v>104</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E146" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G146" s="4">
         <v>0.245472</v>
@@ -7704,16 +7701,16 @@
         <v>104</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G147" s="4">
         <v>0.282416</v>
@@ -7734,16 +7731,16 @@
         <v>104</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G148" s="4">
         <v>0.28014600000000001</v>
@@ -7764,16 +7761,16 @@
         <v>104</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E149" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G149" s="4">
         <v>0.80169999999999997</v>
@@ -7794,16 +7791,16 @@
         <v>104</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G150" s="4">
         <v>0.553118</v>
@@ -7824,16 +7821,16 @@
         <v>104</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G151" s="4">
         <v>0.82854399999999995</v>
@@ -7854,16 +7851,16 @@
         <v>104</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G152" s="4">
         <v>0.61828399999999994</v>
@@ -7884,16 +7881,16 @@
         <v>104</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G153" s="4">
         <v>0.83161499999999999</v>
@@ -7914,16 +7911,16 @@
         <v>104</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G154" s="4">
         <v>0.63358099999999995</v>
@@ -7944,16 +7941,16 @@
         <v>104</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E155" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G155" s="4">
         <v>0.245472</v>
@@ -7974,16 +7971,16 @@
         <v>104</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G156" s="4">
         <v>0.282416</v>
@@ -8004,16 +8001,16 @@
         <v>104</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G157" s="4">
         <v>0.28014600000000001</v>
@@ -8034,16 +8031,16 @@
         <v>104</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E158" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G158" s="4">
         <v>0.80169999999999997</v>
@@ -8064,16 +8061,16 @@
         <v>104</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G159" s="4">
         <v>0.553118</v>
@@ -8094,16 +8091,16 @@
         <v>104</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G160" s="4">
         <v>0.82854399999999995</v>
@@ -8124,16 +8121,16 @@
         <v>104</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G161" s="4">
         <v>0.61828399999999994</v>
@@ -8154,16 +8151,16 @@
         <v>104</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G162" s="4">
         <v>0.83161499999999999</v>
@@ -8184,16 +8181,16 @@
         <v>104</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G163" s="4">
         <v>0.63358099999999995</v>
@@ -8214,16 +8211,16 @@
         <v>114</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E164" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G164" s="4">
         <v>0.245472</v>
@@ -8244,16 +8241,16 @@
         <v>114</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G165" s="4">
         <v>0.282416</v>
@@ -8274,16 +8271,16 @@
         <v>114</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G166" s="4">
         <v>0.28014600000000001</v>
@@ -8304,16 +8301,16 @@
         <v>114</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E167" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G167" s="4">
         <v>0.80169800000000002</v>
@@ -8334,16 +8331,16 @@
         <v>114</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G168" s="4">
         <v>0.55312099999999997</v>
@@ -8364,16 +8361,16 @@
         <v>114</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G169" s="4">
         <v>0.82854399999999995</v>
@@ -8394,16 +8391,16 @@
         <v>114</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G170" s="4">
         <v>0.61828399999999994</v>
@@ -8424,16 +8421,16 @@
         <v>114</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G171" s="4">
         <v>0.83161499999999999</v>
@@ -8454,16 +8451,16 @@
         <v>114</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G172" s="4">
         <v>0.63358099999999995</v>
@@ -8484,16 +8481,16 @@
         <v>120</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E173" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G173" s="4">
         <v>0.245472</v>
@@ -8514,16 +8511,16 @@
         <v>120</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G174" s="4">
         <v>0.282416</v>
@@ -8544,16 +8541,16 @@
         <v>120</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G175" s="4">
         <v>0.28014600000000001</v>
@@ -8574,16 +8571,16 @@
         <v>120</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E176" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G176" s="4">
         <v>0.80169400000000002</v>
@@ -8604,16 +8601,16 @@
         <v>120</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G177" s="4">
         <v>0.55312399999999995</v>
@@ -8634,16 +8631,16 @@
         <v>120</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G178" s="4">
         <v>0.82854399999999995</v>
@@ -8664,16 +8661,16 @@
         <v>120</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G179" s="4">
         <v>0.61828399999999994</v>
@@ -8694,16 +8691,16 @@
         <v>120</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G180" s="4">
         <v>0.83161499999999999</v>
@@ -8724,16 +8721,16 @@
         <v>120</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G181" s="4">
         <v>0.63358099999999995</v>
@@ -8754,16 +8751,16 @@
         <v>120</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E182" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G182" s="4">
         <v>0.245472</v>
@@ -8784,16 +8781,16 @@
         <v>120</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G183" s="4">
         <v>0.282416</v>
@@ -8814,16 +8811,16 @@
         <v>120</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G184" s="4">
         <v>0.28014600000000001</v>
@@ -8844,16 +8841,16 @@
         <v>120</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E185" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G185" s="4">
         <v>0.80169400000000002</v>
@@ -8874,16 +8871,16 @@
         <v>120</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G186" s="4">
         <v>0.55312399999999995</v>
@@ -8904,16 +8901,16 @@
         <v>120</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G187" s="4">
         <v>0.82854399999999995</v>
@@ -8934,16 +8931,16 @@
         <v>120</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G188" s="4">
         <v>0.61828399999999994</v>
@@ -8964,16 +8961,16 @@
         <v>120</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G189" s="4">
         <v>0.83161499999999999</v>
@@ -8994,16 +8991,16 @@
         <v>120</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G190" s="4">
         <v>0.63358099999999995</v>
@@ -9024,16 +9021,16 @@
         <v>131</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E191" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F191" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G191" s="4">
         <v>0.245472</v>
@@ -9054,16 +9051,16 @@
         <v>131</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G192" s="4">
         <v>0.282416</v>
@@ -9084,16 +9081,16 @@
         <v>131</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G193" s="4">
         <v>0.28014600000000001</v>
@@ -9114,16 +9111,16 @@
         <v>131</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E194" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G194" s="4">
         <v>0.80170200000000003</v>
@@ -9144,16 +9141,16 @@
         <v>131</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G195" s="4">
         <v>0.55312099999999997</v>
@@ -9174,16 +9171,16 @@
         <v>131</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G196" s="4">
         <v>0.82854399999999995</v>
@@ -9204,16 +9201,16 @@
         <v>131</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G197" s="4">
         <v>0.61828399999999994</v>
@@ -9234,16 +9231,16 @@
         <v>131</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G198" s="4">
         <v>0.83161499999999999</v>
@@ -9264,16 +9261,16 @@
         <v>131</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G199" s="4">
         <v>0.63358099999999995</v>
@@ -9294,16 +9291,16 @@
         <v>131</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E200" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G200" s="4">
         <v>0.245472</v>
@@ -9324,16 +9321,16 @@
         <v>131</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G201" s="4">
         <v>0.282416</v>
@@ -9354,16 +9351,16 @@
         <v>131</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G202" s="4">
         <v>0.28014600000000001</v>
@@ -9384,16 +9381,16 @@
         <v>131</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E203" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G203" s="4">
         <v>0.80170200000000003</v>
@@ -9414,16 +9411,16 @@
         <v>131</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G204" s="4">
         <v>0.55312099999999997</v>
@@ -9444,16 +9441,16 @@
         <v>131</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G205" s="4">
         <v>0.82854399999999995</v>
@@ -9474,16 +9471,16 @@
         <v>131</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G206" s="4">
         <v>0.61828399999999994</v>
@@ -9504,16 +9501,16 @@
         <v>131</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G207" s="4">
         <v>0.83161499999999999</v>
@@ -9534,16 +9531,16 @@
         <v>131</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G208" s="4">
         <v>0.63358099999999995</v>
@@ -9564,16 +9561,16 @@
         <v>131</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E209" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G209" s="4">
         <v>0.245472</v>
@@ -9594,16 +9591,16 @@
         <v>131</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G210" s="4">
         <v>0.282416</v>
@@ -9624,16 +9621,16 @@
         <v>131</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G211" s="4">
         <v>0.28014600000000001</v>
@@ -9654,16 +9651,16 @@
         <v>131</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E212" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G212" s="4">
         <v>0.80170200000000003</v>
@@ -9684,16 +9681,16 @@
         <v>131</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G213" s="4">
         <v>0.55312099999999997</v>
@@ -9714,16 +9711,16 @@
         <v>131</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G214" s="4">
         <v>0.82854399999999995</v>
@@ -9744,16 +9741,16 @@
         <v>131</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G215" s="4">
         <v>0.61828399999999994</v>
@@ -9774,16 +9771,16 @@
         <v>131</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G216" s="4">
         <v>0.83161499999999999</v>
@@ -9804,16 +9801,16 @@
         <v>131</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G217" s="4">
         <v>0.63358099999999995</v>
@@ -9834,16 +9831,16 @@
         <v>131</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E218" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G218" s="4">
         <v>0.245472</v>
@@ -9864,16 +9861,16 @@
         <v>131</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G219" s="4">
         <v>0.282416</v>
@@ -9894,16 +9891,16 @@
         <v>131</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G220" s="4">
         <v>0.28014600000000001</v>
@@ -9924,16 +9921,16 @@
         <v>131</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E221" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G221" s="4">
         <v>0.80170200000000003</v>
@@ -9954,16 +9951,16 @@
         <v>131</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G222" s="4">
         <v>0.55312099999999997</v>
@@ -9984,16 +9981,16 @@
         <v>131</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G223" s="4">
         <v>0.82854399999999995</v>
@@ -10014,16 +10011,16 @@
         <v>131</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G224" s="4">
         <v>0.61828399999999994</v>
@@ -10044,16 +10041,16 @@
         <v>131</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G225" s="4">
         <v>0.83161499999999999</v>
@@ -10074,16 +10071,16 @@
         <v>131</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G226" s="4">
         <v>0.63358099999999995</v>
@@ -10104,16 +10101,16 @@
         <v>147</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E227" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G227" s="4">
         <v>0.31461099999999997</v>
@@ -10134,16 +10131,16 @@
         <v>147</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G228" s="4">
         <v>0.36653999999999998</v>
@@ -10164,16 +10161,16 @@
         <v>147</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G229" s="4">
         <v>0.34986600000000001</v>
@@ -10194,16 +10191,16 @@
         <v>147</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E230" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G230" s="4">
         <v>0.79687799999999998</v>
@@ -10224,16 +10221,16 @@
         <v>147</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G231" s="4">
         <v>0.56104900000000002</v>
@@ -10254,16 +10251,16 @@
         <v>147</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G232" s="4">
         <v>0.82152199999999997</v>
@@ -10284,16 +10281,16 @@
         <v>147</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G233" s="4">
         <v>0.61744399999999999</v>
@@ -10314,16 +10311,16 @@
         <v>147</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G234" s="4">
         <v>0.82388600000000001</v>
@@ -10344,16 +10341,16 @@
         <v>147</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G235" s="4">
         <v>0.63169399999999998</v>
@@ -10374,16 +10371,16 @@
         <v>151</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E236" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G236" s="4">
         <v>0.3599</v>
@@ -10404,16 +10401,16 @@
         <v>151</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E237" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G237" s="4">
         <v>0.35105799999999998</v>
@@ -10434,16 +10431,16 @@
         <v>151</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D238" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D238" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E238" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G238" s="4">
         <v>0.32555699999999999</v>
@@ -10464,16 +10461,16 @@
         <v>151</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D239" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E239" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G239" s="4">
         <v>0.81636699999999995</v>
@@ -10494,16 +10491,16 @@
         <v>151</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E240" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G240" s="4">
         <v>0.55715800000000004</v>
@@ -10524,16 +10521,16 @@
         <v>151</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D241" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E241" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G241" s="4">
         <v>0.83724399999999999</v>
@@ -10554,16 +10551,16 @@
         <v>151</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D242" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E242" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G242" s="4">
         <v>0.61881200000000003</v>
@@ -10584,16 +10581,16 @@
         <v>151</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D243" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E243" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G243" s="4">
         <v>0.83833299999999999</v>
@@ -10614,16 +10611,16 @@
         <v>151</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D244" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E244" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G244" s="4">
         <v>0.63338399999999995</v>
@@ -10644,16 +10641,16 @@
         <v>154</v>
       </c>
       <c r="C245" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D245" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E245" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G245" s="4">
         <v>0.24327699999999999</v>
@@ -10674,16 +10671,16 @@
         <v>154</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D246" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E246" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G246" s="4">
         <v>0.34002199999999999</v>
@@ -10704,16 +10701,16 @@
         <v>154</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D247" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E247" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G247" s="4">
         <v>0.33022400000000002</v>
@@ -10734,16 +10731,16 @@
         <v>154</v>
       </c>
       <c r="C248" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D248" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D248" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E248" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G248" s="4">
         <v>0.79859000000000002</v>
@@ -10764,16 +10761,16 @@
         <v>154</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D249" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E249" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G249" s="4">
         <v>0.51651000000000002</v>
@@ -10794,16 +10791,16 @@
         <v>154</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D250" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E250" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G250" s="4">
         <v>0.83457499999999996</v>
@@ -10824,16 +10821,16 @@
         <v>154</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E251" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G251" s="4">
         <v>0.62294300000000002</v>
@@ -10854,16 +10851,16 @@
         <v>154</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D252" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E252" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G252" s="4">
         <v>0.83736999999999995</v>
@@ -10884,16 +10881,16 @@
         <v>154</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D253" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E253" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G253" s="4">
         <v>0.63007999999999997</v>
@@ -10914,16 +10911,16 @@
         <v>147</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E254" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G254" s="4">
         <v>0.31461099999999997</v>
@@ -10944,16 +10941,16 @@
         <v>147</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G255" s="4">
         <v>0.36653999999999998</v>
@@ -10974,16 +10971,16 @@
         <v>147</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G256" s="4">
         <v>0.34986600000000001</v>
@@ -11004,16 +11001,16 @@
         <v>147</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E257" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G257" s="4">
         <v>0.79687799999999998</v>
@@ -11034,16 +11031,16 @@
         <v>147</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G258" s="4">
         <v>0.56104900000000002</v>
@@ -11064,16 +11061,16 @@
         <v>147</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G259" s="4">
         <v>0.82152199999999997</v>
@@ -11094,16 +11091,16 @@
         <v>147</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G260" s="4">
         <v>0.61744399999999999</v>
@@ -11124,16 +11121,16 @@
         <v>147</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G261" s="4">
         <v>0.82388600000000001</v>
@@ -11154,16 +11151,16 @@
         <v>147</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G262" s="4">
         <v>0.63169399999999998</v>
@@ -11184,16 +11181,16 @@
         <v>151</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E263" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G263" s="4">
         <v>0.3599</v>
@@ -11214,16 +11211,16 @@
         <v>151</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G264" s="4">
         <v>0.35105799999999998</v>
@@ -11244,16 +11241,16 @@
         <v>151</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G265" s="4">
         <v>0.32555699999999999</v>
@@ -11274,16 +11271,16 @@
         <v>151</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E266" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G266" s="4">
         <v>0.81636699999999995</v>
@@ -11304,16 +11301,16 @@
         <v>151</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G267" s="4">
         <v>0.55715800000000004</v>
@@ -11334,16 +11331,16 @@
         <v>151</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G268" s="4">
         <v>0.83724399999999999</v>
@@ -11364,16 +11361,16 @@
         <v>151</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G269" s="4">
         <v>0.61881200000000003</v>
@@ -11394,16 +11391,16 @@
         <v>151</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G270" s="4">
         <v>0.83833299999999999</v>
@@ -11424,16 +11421,16 @@
         <v>151</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G271" s="4">
         <v>0.63338399999999995</v>
@@ -11454,16 +11451,16 @@
         <v>154</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E272" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F272" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G272" s="4">
         <v>0.24327699999999999</v>
@@ -11484,16 +11481,16 @@
         <v>154</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G273" s="4">
         <v>0.34002199999999999</v>
@@ -11514,16 +11511,16 @@
         <v>154</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G274" s="4">
         <v>0.33022400000000002</v>
@@ -11544,16 +11541,16 @@
         <v>154</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E275" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G275" s="4">
         <v>0.79859000000000002</v>
@@ -11574,16 +11571,16 @@
         <v>154</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G276" s="4">
         <v>0.51651000000000002</v>
@@ -11604,16 +11601,16 @@
         <v>154</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G277" s="4">
         <v>0.83457499999999996</v>
@@ -11634,16 +11631,16 @@
         <v>154</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G278" s="4">
         <v>0.62294300000000002</v>
@@ -11664,16 +11661,16 @@
         <v>154</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G279" s="4">
         <v>0.83736999999999995</v>
@@ -11694,16 +11691,16 @@
         <v>154</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G280" s="4">
         <v>0.63007999999999997</v>
@@ -11724,16 +11721,16 @@
         <v>147</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E281" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G281" s="4">
         <v>0.31461099999999997</v>
@@ -11754,16 +11751,16 @@
         <v>147</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G282" s="4">
         <v>0.36653999999999998</v>
@@ -11784,16 +11781,16 @@
         <v>147</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G283" s="4">
         <v>0.34986600000000001</v>
@@ -11814,16 +11811,16 @@
         <v>147</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E284" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G284" s="4">
         <v>0.79687799999999998</v>
@@ -11844,16 +11841,16 @@
         <v>147</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G285" s="4">
         <v>0.56104900000000002</v>
@@ -11874,16 +11871,16 @@
         <v>147</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G286" s="4">
         <v>0.82152199999999997</v>
@@ -11904,16 +11901,16 @@
         <v>147</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G287" s="4">
         <v>0.61744399999999999</v>
@@ -11934,16 +11931,16 @@
         <v>147</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G288" s="4">
         <v>0.82388600000000001</v>
@@ -11964,16 +11961,16 @@
         <v>147</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G289" s="4">
         <v>0.63169399999999998</v>
@@ -11994,16 +11991,16 @@
         <v>170</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E290" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G290" s="4">
         <v>0.245472</v>
@@ -12024,16 +12021,16 @@
         <v>170</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G291" s="4">
         <v>0.282416</v>
@@ -12054,16 +12051,16 @@
         <v>170</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G292" s="4">
         <v>0.28014600000000001</v>
@@ -12084,16 +12081,16 @@
         <v>170</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E293" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G293" s="4">
         <v>0.80170600000000003</v>
@@ -12114,16 +12111,16 @@
         <v>170</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G294" s="4">
         <v>0.55311699999999997</v>
@@ -12144,16 +12141,16 @@
         <v>170</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G295" s="4">
         <v>0.82854399999999995</v>
@@ -12174,16 +12171,16 @@
         <v>170</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G296" s="4">
         <v>0.61828399999999994</v>
@@ -12204,16 +12201,16 @@
         <v>170</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G297" s="4">
         <v>0.83161499999999999</v>
@@ -12234,16 +12231,16 @@
         <v>170</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G298" s="4">
         <v>0.63358099999999995</v>
@@ -12264,16 +12261,16 @@
         <v>170</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E299" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F299" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G299" s="4">
         <v>0.245472</v>
@@ -12294,16 +12291,16 @@
         <v>170</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G300" s="4">
         <v>0.282416</v>
@@ -12324,16 +12321,16 @@
         <v>170</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G301" s="4">
         <v>0.28014600000000001</v>
@@ -12354,16 +12351,16 @@
         <v>170</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E302" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F302" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G302" s="4">
         <v>0.80170600000000003</v>
@@ -12384,16 +12381,16 @@
         <v>170</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G303" s="4">
         <v>0.55311699999999997</v>
@@ -12414,16 +12411,16 @@
         <v>170</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G304" s="4">
         <v>0.82854399999999995</v>
@@ -12444,16 +12441,16 @@
         <v>170</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G305" s="4">
         <v>0.61828399999999994</v>
@@ -12474,16 +12471,16 @@
         <v>170</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G306" s="4">
         <v>0.83161499999999999</v>
@@ -12504,16 +12501,16 @@
         <v>170</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G307" s="4">
         <v>0.63358099999999995</v>
@@ -12534,16 +12531,16 @@
         <v>180</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D308" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="E308" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G308" s="4">
         <v>0.44441799999999998</v>
@@ -12564,16 +12561,16 @@
         <v>180</v>
       </c>
       <c r="C309" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D309" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D309" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="E309" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G309" s="4">
         <v>0.40514899999999998</v>
@@ -12594,16 +12591,16 @@
         <v>180</v>
       </c>
       <c r="C310" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D310" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D310" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="E310" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G310" s="4">
         <v>0.42920700000000001</v>
@@ -12624,16 +12621,16 @@
         <v>180</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E311" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F311" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G311" s="4">
         <v>0.44441799999999998</v>
@@ -12654,16 +12651,16 @@
         <v>180</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G312" s="4">
         <v>0.40514899999999998</v>
@@ -12684,16 +12681,16 @@
         <v>180</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G313" s="4">
         <v>0.42920700000000001</v>
@@ -12714,16 +12711,16 @@
         <v>188</v>
       </c>
       <c r="C314" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D314" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D314" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="E314" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F314" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G314" s="4">
         <v>0.46855400000000003</v>
@@ -12744,16 +12741,16 @@
         <v>188</v>
       </c>
       <c r="C315" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D315" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D315" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="E315" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G315" s="4">
         <v>0.405422</v>
@@ -12774,16 +12771,16 @@
         <v>188</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D316" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="E316" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G316" s="4">
         <v>0.42799900000000002</v>
@@ -12804,16 +12801,16 @@
         <v>188</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E317" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F317" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G317" s="4">
         <v>0.46855400000000003</v>
@@ -12834,16 +12831,16 @@
         <v>188</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G318" s="4">
         <v>0.405422</v>
@@ -12864,16 +12861,16 @@
         <v>188</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G319" s="4">
         <v>0.42799900000000002</v>
@@ -12894,16 +12891,16 @@
         <v>197</v>
       </c>
       <c r="C320" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D320" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D320" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E320" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F320" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G320" s="4">
         <v>0.474468</v>
@@ -12924,16 +12921,16 @@
         <v>197</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D321" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E321" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G321" s="4">
         <v>0.41612700000000002</v>
@@ -12954,16 +12951,16 @@
         <v>197</v>
       </c>
       <c r="C322" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D322" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D322" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E322" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G322" s="4">
         <v>0.444492</v>
@@ -12984,16 +12981,16 @@
         <v>197</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E323" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F323" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G323" s="4">
         <v>0.474468</v>
@@ -13014,16 +13011,16 @@
         <v>197</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G324" s="4">
         <v>0.41612700000000002</v>
@@ -13044,16 +13041,16 @@
         <v>197</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G325" s="4">
         <v>0.444492</v>
@@ -13074,16 +13071,16 @@
         <v>207</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E326" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F326" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G326" s="4">
         <v>0.474468</v>
@@ -13104,16 +13101,16 @@
         <v>207</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G327" s="4">
         <v>0.41612700000000002</v>
@@ -13134,16 +13131,16 @@
         <v>207</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G328" s="4">
         <v>0.444492</v>
@@ -13164,16 +13161,16 @@
         <v>207</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E329" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F329" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F329" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G329" s="4">
         <v>0.474468</v>
@@ -13194,16 +13191,16 @@
         <v>207</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G330" s="4">
         <v>0.41612700000000002</v>
@@ -13224,16 +13221,16 @@
         <v>207</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G331" s="4">
         <v>0.444492</v>
@@ -13265,7 +13262,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -13274,54 +13271,54 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
@@ -13330,26 +13327,26 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
@@ -13358,12 +13355,12 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
@@ -13372,21 +13369,21 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -13405,47 +13402,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/feature_ablation.xlsx
+++ b/experiments/feature_ablation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BigData\experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7389ED2-A495-4418-B6E8-4226E84BDC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEFE83D-8A55-4420-9695-256E46E350BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3310" yWindow="2210" windowWidth="19200" windowHeight="11710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Bỏ theo EDA'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chi tiết'!$A$1:$I$331</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng hợp'!$A$1:$M$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chi tiết'!$A$1:$I$349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tổng hợp'!$A$1:$M$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2505" uniqueCount="307">
   <si>
     <t>ID</t>
   </si>
@@ -568,6 +568,48 @@
     <t>Gần không PCA cho model tuyến tính; cây vẫn tốt nhất khi không PCA</t>
   </si>
   <si>
+    <t>K13a</t>
+  </si>
+  <si>
+    <t>C (và A)</t>
+  </si>
+  <si>
+    <t>Chặn trần độ trễ chuyến trước ở 60 phút</t>
+  </si>
+  <si>
+    <t>prev_arr_delay, inbound_overrun (trần 60)</t>
+  </si>
+  <si>
+    <t>Dùng cho bài C</t>
+  </si>
+  <si>
+    <t>Từ 30 phút tỷ lệ trễ nặng bão hòa 99.7%; LinearSVC AUC-PR +0.029, cây hòa. GBT regressor +0.018 là do CV đổi maxBins</t>
+  </si>
+  <si>
+    <t>kaggle-check-cap60-20260930</t>
+  </si>
+  <si>
+    <t>K13b</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Chặn trần độ trễ chuyến trước ở 300 phút</t>
+  </si>
+  <si>
+    <t>prev_arr_delay, inbound_overrun (trần 300)</t>
+  </si>
+  <si>
+    <t>Dùng cho bài A</t>
+  </si>
+  <si>
+    <t>Trễ tăng khoảng 1:1 tới 5 tiếng rồi gãy; LinearRegression R² +0.0045, RF +0.0028, GBT y hệt, classifier y hệt</t>
+  </si>
+  <si>
+    <t>kaggle-check-cap300-20260930</t>
+  </si>
+  <si>
     <t>G1</t>
   </si>
   <si>
@@ -797,6 +839,15 @@
   </si>
   <si>
     <t>kg-v2_pca_numeric</t>
+  </si>
+  <si>
+    <t>kg-v3</t>
+  </si>
+  <si>
+    <t>kg-v3_cap60</t>
+  </si>
+  <si>
+    <t>kg-v3_cap300</t>
   </si>
   <si>
     <t>kg-gain</t>
@@ -1312,7 +1363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="7" customWidth="1"/>
@@ -1384,23 +1435,23 @@
         <v>17</v>
       </c>
       <c r="F2" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A2,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A2,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>5.6163333333333334E-3</v>
       </c>
       <c r="G2" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A2,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A2,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-6.763333333333158E-4</v>
       </c>
       <c r="H2" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A2,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A2,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-7.8933333333333633E-4</v>
       </c>
       <c r="I2" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A2)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A2)</f>
         <v>-3.6370000000000013E-3</v>
       </c>
       <c r="J2" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A2)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A2)</f>
         <v>1.6795999999999998E-2</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -1430,23 +1481,23 @@
         <v>24</v>
       </c>
       <c r="F3" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A3,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A3,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>3.1766333333333334E-2</v>
       </c>
       <c r="G3" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A3,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A3,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>2.3845333333333312E-2</v>
       </c>
       <c r="H3" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A3,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A3,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>5.668433333333333E-2</v>
       </c>
       <c r="I3" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A3)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A3)</f>
         <v>7.1020000000000007E-3</v>
       </c>
       <c r="J3" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A3)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A3)</f>
         <v>8.2457999999999976E-2</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -1476,23 +1527,23 @@
         <v>30</v>
       </c>
       <c r="F4" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A4,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A4,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>0.19570299999999996</v>
       </c>
       <c r="G4" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A4,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A4,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>0.12931999999999999</v>
       </c>
       <c r="H4" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A4,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A4,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>0.28043266666666672</v>
       </c>
       <c r="I4" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A4)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A4)</f>
         <v>0.12757699999999994</v>
       </c>
       <c r="J4" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A4)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A4)</f>
         <v>0.302089</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -1522,23 +1573,23 @@
         <v>24</v>
       </c>
       <c r="F5" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A5,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A5,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>5.6177000000000012E-2</v>
       </c>
       <c r="G5" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A5,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A5,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>2.7357333333333345E-2</v>
       </c>
       <c r="H5" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A5,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A5,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>7.1523666666666666E-2</v>
       </c>
       <c r="I5" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A5)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A5)</f>
         <v>1.8716999999999984E-2</v>
       </c>
       <c r="J5" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A5)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A5)</f>
         <v>9.4052000000000024E-2</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -1568,23 +1619,23 @@
         <v>41</v>
       </c>
       <c r="F6" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A6,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A6,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>1.9299999999999873E-4</v>
       </c>
       <c r="G6" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A6,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A6,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-8.7399999999996736E-4</v>
       </c>
       <c r="H6" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A6,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A6,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-2.4133333333331564E-4</v>
       </c>
       <c r="I6" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A6)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A6)</f>
         <v>-3.1990000000000629E-3</v>
       </c>
       <c r="J6" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A6)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A6)</f>
         <v>5.4150000000000587E-3</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -1614,23 +1665,23 @@
         <v>47</v>
       </c>
       <c r="F7" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A7,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A7,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.3487000000000008E-2</v>
       </c>
       <c r="G7" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A7,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A7,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-7.46566666666663E-3</v>
       </c>
       <c r="H7" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A7,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A7,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-4.0279999999999943E-3</v>
       </c>
       <c r="I7" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A7)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A7)</f>
         <v>-1.7207000000000028E-2</v>
       </c>
       <c r="J7" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A7)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A7)</f>
         <v>6.3480000000000203E-3</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -1660,23 +1711,23 @@
         <v>17</v>
       </c>
       <c r="F8" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A8,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A8,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>4.2506666666666682E-3</v>
       </c>
       <c r="G8" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A8,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A8,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>1.3906666666666883E-3</v>
       </c>
       <c r="H8" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A8,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A8,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.4460000000000028E-3</v>
       </c>
       <c r="I8" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A8)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A8)</f>
         <v>-3.9649999999999963E-3</v>
       </c>
       <c r="J8" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A8)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A8)</f>
         <v>1.1101000000000001E-2</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -1706,23 +1757,23 @@
         <v>17</v>
       </c>
       <c r="F9" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A9,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A9,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>2.1340000000000018E-3</v>
       </c>
       <c r="G9" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A9,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A9,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.5609999999999975E-3</v>
       </c>
       <c r="H9" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A9,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A9,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-5.3899999999999877E-3</v>
       </c>
       <c r="I9" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A9)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A9)</f>
         <v>-1.1854000000000003E-2</v>
       </c>
       <c r="J9" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A9)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A9)</f>
         <v>7.4430000000000052E-3</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -1752,23 +1803,23 @@
         <v>17</v>
       </c>
       <c r="F10" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A10,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A10,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-2.1500000000000039E-3</v>
       </c>
       <c r="G10" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A10,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A10,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>3.6566666666670855E-4</v>
       </c>
       <c r="H10" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A10,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A10,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-2.083333333333289E-4</v>
       </c>
       <c r="I10" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A10)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A10)</f>
         <v>-8.6689999999999823E-3</v>
       </c>
       <c r="J10" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A10)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A10)</f>
         <v>1.7919999999999603E-3</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -1798,23 +1849,23 @@
         <v>17</v>
       </c>
       <c r="F11" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A11,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A11,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-4.1629999999999905E-3</v>
       </c>
       <c r="G11" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A11,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A11,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-2.4200000000000146E-4</v>
       </c>
       <c r="H11" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A11,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A11,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.7133333333330114E-4</v>
       </c>
       <c r="I11" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A11)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A11)</f>
         <v>-9.9579999999999669E-3</v>
       </c>
       <c r="J11" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A11)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A11)</f>
         <v>7.5000000000002842E-4</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -1844,23 +1895,23 @@
         <v>17</v>
       </c>
       <c r="F12" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A12,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A12,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.936999999999985E-3</v>
       </c>
       <c r="G12" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A12,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A12,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>2.4409999999999896E-3</v>
       </c>
       <c r="H12" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A12,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A12,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>9.1300000000001569E-4</v>
       </c>
       <c r="I12" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A12)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A12)</f>
         <v>-4.7449999999999992E-3</v>
       </c>
       <c r="J12" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A12)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A12)</f>
         <v>4.4359999999999955E-3</v>
       </c>
       <c r="K12" s="2" t="s">
@@ -1890,23 +1941,23 @@
         <v>75</v>
       </c>
       <c r="F13" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A13,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A13,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.3389999999999975E-3</v>
       </c>
       <c r="G13" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A13,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A13,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>9.5966666666665501E-4</v>
       </c>
       <c r="H13" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A13,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A13,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>2.1500000000000221E-3</v>
       </c>
       <c r="I13" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A13)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A13)</f>
         <v>-3.1930000000000014E-3</v>
       </c>
       <c r="J13" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A13)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A13)</f>
         <v>4.0120000000000156E-3</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -1936,23 +1987,23 @@
         <v>17</v>
       </c>
       <c r="F14" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A14,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A14,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-8.1246666666666672E-3</v>
       </c>
       <c r="G14" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A14,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A14,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-6.0433333333333632E-3</v>
       </c>
       <c r="H14" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A14,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A14,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-5.095999999999999E-3</v>
       </c>
       <c r="I14" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A14)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A14)</f>
         <v>-2.1074000000000002E-2</v>
       </c>
       <c r="J14" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A14)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A14)</f>
         <v>5.9999999999993392E-4</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -1982,23 +2033,23 @@
         <v>86</v>
       </c>
       <c r="F15" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A15,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A15,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>6.2366666666667048E-4</v>
       </c>
       <c r="G15" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A15,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A15,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>9.6166666666671252E-4</v>
       </c>
       <c r="H15" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A15,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A15,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>4.5560000000000418E-3</v>
       </c>
       <c r="I15" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A15)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A15)</f>
         <v>-1.0330000000000061E-3</v>
       </c>
       <c r="J15" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A15)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A15)</f>
         <v>6.3220000000000498E-3</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -2028,23 +2079,23 @@
         <v>17</v>
       </c>
       <c r="F16" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A16,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A16,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-4.7233333333333388E-4</v>
       </c>
       <c r="G16" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A16,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A16,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.7763333333333058E-3</v>
       </c>
       <c r="H16" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A16,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A16,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-2.006666666665898E-4</v>
       </c>
       <c r="I16" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A16)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A16)</f>
         <v>-3.8159999999999306E-3</v>
       </c>
       <c r="J16" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A16)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A16)</f>
         <v>5.3200000000008796E-4</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -2074,23 +2125,23 @@
         <v>24</v>
       </c>
       <c r="F17" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A17,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A17,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.732000000000002E-3</v>
       </c>
       <c r="G17" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A17,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A17,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-4.7266666666666195E-3</v>
       </c>
       <c r="H17" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A17,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A17,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-2.0266666666661029E-4</v>
       </c>
       <c r="I17" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A17)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A17)</f>
         <v>-9.4419999999999504E-3</v>
       </c>
       <c r="J17" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A17)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A17)</f>
         <v>1.8000000000006899E-4</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -2120,23 +2171,23 @@
         <v>102</v>
       </c>
       <c r="F18" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A18,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A18,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-6.1316666666666741E-3</v>
       </c>
       <c r="G18" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A18,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A18,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-8.9399999999998736E-4</v>
       </c>
       <c r="H18" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A18,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A18,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.8173333333332635E-3</v>
       </c>
       <c r="I18" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A18)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A18)</f>
         <v>-1.7877000000000032E-2</v>
       </c>
       <c r="J18" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A18)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A18)</f>
         <v>6.0000000000060005E-6</v>
       </c>
       <c r="K18" s="2" t="s">
@@ -2166,23 +2217,23 @@
         <v>24</v>
       </c>
       <c r="F19" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A19,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A19,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.3169999999999942E-3</v>
       </c>
       <c r="G19" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A19,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A19,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-2.4483333333333115E-3</v>
       </c>
       <c r="H19" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A19,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A19,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>3.890000000000467E-4</v>
       </c>
       <c r="I19" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A19)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A19)</f>
         <v>-2.8070000000000039E-3</v>
       </c>
       <c r="J19" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A19)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A19)</f>
         <v>1.3980000000000103E-3</v>
       </c>
       <c r="K19" s="2" t="s">
@@ -2212,23 +2263,23 @@
         <v>112</v>
       </c>
       <c r="F20" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A20,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A20,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.4049999999999989E-3</v>
       </c>
       <c r="G20" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A20,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A20,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-8.6133333333326956E-4</v>
       </c>
       <c r="H20" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A20,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A20,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-5.9899999999994214E-4</v>
       </c>
       <c r="I20" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A20)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A20)</f>
         <v>-2.7529999999998944E-3</v>
       </c>
       <c r="J20" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A20)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A20)</f>
         <v>3.1100000000006123E-4</v>
       </c>
       <c r="K20" s="2" t="s">
@@ -2258,23 +2309,23 @@
         <v>118</v>
       </c>
       <c r="F21" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A21,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A21,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-8.3933333333332161E-4</v>
       </c>
       <c r="G21" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A21,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A21,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>5.8799999999999597E-4</v>
       </c>
       <c r="H21" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A21,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A21,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>2.5723333333333986E-3</v>
       </c>
       <c r="I21" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A21)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A21)</f>
         <v>-3.3449999999999869E-3</v>
       </c>
       <c r="J21" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A21)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A21)</f>
         <v>4.7410000000001062E-3</v>
       </c>
       <c r="K21" s="2" t="s">
@@ -2304,23 +2355,23 @@
         <v>124</v>
       </c>
       <c r="F22" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A22,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A22,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-6.0933333333333299E-3</v>
       </c>
       <c r="G22" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A22,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A22,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.3919999999999859E-3</v>
       </c>
       <c r="H22" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A22,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A22,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.6879999999999489E-3</v>
       </c>
       <c r="I22" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A22)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A22)</f>
         <v>-1.7591999999999997E-2</v>
       </c>
       <c r="J22" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A22)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A22)</f>
         <v>2.9299999999998771E-4</v>
       </c>
       <c r="K22" s="2" t="s">
@@ -2350,23 +2401,23 @@
         <v>129</v>
       </c>
       <c r="F23" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A23,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A23,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-6.8290000000000017E-3</v>
       </c>
       <c r="G23" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A23,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A23,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.3233333333333059E-3</v>
       </c>
       <c r="H23" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A23,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A23,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>1.7170000000000425E-3</v>
       </c>
       <c r="I23" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A23)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A23)</f>
         <v>-1.7506000000000022E-2</v>
       </c>
       <c r="J23" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A23)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A23)</f>
         <v>7.9620000000000246E-3</v>
       </c>
       <c r="K23" s="2" t="s">
@@ -2396,23 +2447,23 @@
         <v>24</v>
       </c>
       <c r="F24" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A24,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A24,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-5.8063333333333396E-3</v>
       </c>
       <c r="G24" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A24,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A24,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-2.2330000000000036E-3</v>
       </c>
       <c r="H24" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A24,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A24,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.9683333333332755E-3</v>
       </c>
       <c r="I24" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A24)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A24)</f>
         <v>-1.5865000000000018E-2</v>
       </c>
       <c r="J24" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A24)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A24)</f>
         <v>2.8900000000009474E-4</v>
       </c>
       <c r="K24" s="2" t="s">
@@ -2442,23 +2493,23 @@
         <v>24</v>
       </c>
       <c r="F25" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A25,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A25,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-8.9920000000000087E-3</v>
       </c>
       <c r="G25" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A25,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A25,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.3169999999999979E-2</v>
       </c>
       <c r="H25" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A25,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A25,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-1.0238333333333275E-2</v>
       </c>
       <c r="I25" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A25)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A25)</f>
         <v>-1.8931000000000031E-2</v>
       </c>
       <c r="J25" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A25)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A25)</f>
         <v>-2.1840000000000193E-3</v>
       </c>
       <c r="K25" s="2" t="s">
@@ -2488,23 +2539,23 @@
         <v>17</v>
       </c>
       <c r="F26" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A26,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A26,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.6616666666666817E-3</v>
       </c>
       <c r="G26" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A26,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A26,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.067666666666615E-3</v>
       </c>
       <c r="H26" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A26,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A26,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>1.8766666666669707E-4</v>
       </c>
       <c r="I26" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A26)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A26)</f>
         <v>-3.0180000000000207E-3</v>
       </c>
       <c r="J26" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A26)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A26)</f>
         <v>1.6300000000000203E-3</v>
       </c>
       <c r="K26" s="2" t="s">
@@ -2534,23 +2585,23 @@
         <v>17</v>
       </c>
       <c r="F27" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A27,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A27,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>3.2803333333333482E-3</v>
       </c>
       <c r="G27" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A27,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A27,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-3.7499999999997719E-4</v>
       </c>
       <c r="H27" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A27,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A27,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>9.5633333333333681E-4</v>
       </c>
       <c r="I27" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A27)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A27)</f>
         <v>-1.734999999999931E-3</v>
       </c>
       <c r="J27" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A27)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A27)</f>
         <v>9.9520000000000164E-3</v>
       </c>
       <c r="K27" s="2" t="s">
@@ -2580,23 +2631,23 @@
         <v>17</v>
       </c>
       <c r="F28" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A28,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A28,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>1.0793333333333395E-3</v>
       </c>
       <c r="G28" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A28,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A28,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.999999999946489E-6</v>
       </c>
       <c r="H28" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A28,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A28,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>1.0533333333333506E-3</v>
       </c>
       <c r="I28" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A28)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A28)</f>
         <v>-1.1970000000000036E-3</v>
       </c>
       <c r="J28" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A28)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A28)</f>
         <v>3.1970000000000054E-3</v>
       </c>
       <c r="K28" s="2" t="s">
@@ -2626,23 +2677,23 @@
         <v>17</v>
       </c>
       <c r="F29" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A29,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A29,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>9.0433333333334032E-4</v>
       </c>
       <c r="G29" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A29,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A29,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-7.689999999999827E-4</v>
       </c>
       <c r="H29" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A29,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A29,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>1.6893333333333576E-3</v>
       </c>
       <c r="I29" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A29)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A29)</f>
         <v>-1.3279999999999959E-3</v>
       </c>
       <c r="J29" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A29)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A29)</f>
         <v>2.163000000000026E-3</v>
       </c>
       <c r="K29" s="2" t="s">
@@ -2672,23 +2723,23 @@
         <v>118</v>
       </c>
       <c r="F30" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A30,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A30,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>2.9886666666666764E-3</v>
       </c>
       <c r="G30" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A30,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A30,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>1.3133333333333516E-4</v>
       </c>
       <c r="H30" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A30,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A30,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>1.0023333333333273E-3</v>
       </c>
       <c r="I30" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A30)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A30)</f>
         <v>-2.7509999999999479E-3</v>
       </c>
       <c r="J30" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A30)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A30)</f>
         <v>1.1430999999999969E-2</v>
       </c>
       <c r="K30" s="2" t="s">
@@ -2718,23 +2769,23 @@
         <v>118</v>
       </c>
       <c r="F31" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A31,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A31,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>7.2396666666666625E-3</v>
       </c>
       <c r="G31" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A31,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A31,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>9.8733333333337714E-4</v>
       </c>
       <c r="H31" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A31,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A31,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>3.0523333333333604E-3</v>
       </c>
       <c r="I31" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A31)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A31)</f>
         <v>-1.4339999999999908E-3</v>
       </c>
       <c r="J31" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A31)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A31)</f>
         <v>2.1892999999999996E-2</v>
       </c>
       <c r="K31" s="2"/>
@@ -2762,23 +2813,23 @@
         <v>118</v>
       </c>
       <c r="F32" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A32,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A32,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>1.7080000000000057E-3</v>
       </c>
       <c r="G32" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A32,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A32,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-3.1999999999957986E-5</v>
       </c>
       <c r="H32" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A32,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A32,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>6.1103333333333287E-3</v>
       </c>
       <c r="I32" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A32)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A32)</f>
         <v>-3.1449999999999534E-3</v>
       </c>
       <c r="J32" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A32)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A32)</f>
         <v>1.8764000000000003E-2</v>
       </c>
       <c r="K32" s="2"/>
@@ -2806,23 +2857,23 @@
         <v>24</v>
       </c>
       <c r="F33" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A33,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A33,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-0.29153899999999999</v>
       </c>
       <c r="G33" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A33,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A33,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-0.14995366666666665</v>
       </c>
       <c r="H33" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A33,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A33,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-0.349524</v>
       </c>
       <c r="I33" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A33)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A33)</f>
         <v>-0.35128700000000002</v>
       </c>
       <c r="J33" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A33)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A33)</f>
         <v>-0.14838200000000001</v>
       </c>
       <c r="K33" s="2" t="s">
@@ -2852,23 +2903,23 @@
         <v>168</v>
       </c>
       <c r="F34" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A34,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A34,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-3.5553666666666671E-2</v>
       </c>
       <c r="G34" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A34,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A34,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-3.1737666666666629E-2</v>
       </c>
       <c r="H34" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A34,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A34,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-4.5124666666666591E-2</v>
       </c>
       <c r="I34" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A34)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A34)</f>
         <v>-7.2059999999999902E-2</v>
       </c>
       <c r="J34" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A34)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A34)</f>
         <v>1.6270000000000451E-3</v>
       </c>
       <c r="K34" s="2" t="s">
@@ -2898,23 +2949,23 @@
         <v>173</v>
       </c>
       <c r="F35" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A35,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A35,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
         <v>-1.111733333333334E-2</v>
       </c>
       <c r="G35" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A35,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A35,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v>-1.4135000000000009E-2</v>
       </c>
       <c r="H35" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A35,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A35,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v>-2.2303666666666611E-2</v>
       </c>
       <c r="I35" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A35)</f>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A35)</f>
         <v>-4.2042999999999942E-2</v>
       </c>
       <c r="J35" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A35)</f>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A35)</f>
         <v>1.5059000000000045E-2</v>
       </c>
       <c r="K35" s="2" t="s">
@@ -2927,7 +2978,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" ht="42" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>175</v>
       </c>
@@ -2941,171 +2992,171 @@
         <v>178</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="F36" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A36,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>-3.1303333333333329E-2</v>
-      </c>
-      <c r="G36" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A36,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A36,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
-        <v/>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A36,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>7.6476666666666637E-3</v>
+      </c>
+      <c r="G36" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A36,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
+        <v>1.2350000000000232E-3</v>
+      </c>
+      <c r="H36" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A36,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
+        <v>1.1046333333333344E-2</v>
       </c>
       <c r="I36" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A36)</f>
-        <v>-6.4641000000000004E-2</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A36)</f>
+        <v>-1.5789999999999971E-3</v>
       </c>
       <c r="J36" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A36)</f>
-        <v>-9.099999999999997E-3</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A36)</f>
+        <v>2.8710000000000013E-2</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="F37" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A37,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>7.7336666666666942E-3</v>
-      </c>
-      <c r="G37" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A37,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A37,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
-        <v/>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A37,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>2.4593333333333134E-3</v>
+      </c>
+      <c r="G37" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A37,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
+        <v>-4.3333333333099118E-6</v>
+      </c>
+      <c r="H37" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A37,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
+        <v>1.1400000000002149E-4</v>
       </c>
       <c r="I37" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A37)</f>
-        <v>-1.2079999999999869E-3</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A37)</f>
+        <v>-8.0000000000080007E-6</v>
       </c>
       <c r="J37" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A37)</f>
-        <v>2.4136000000000046E-2</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A37)</f>
+        <v>4.573999999999967E-3</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>168</v>
+        <v>24</v>
       </c>
       <c r="F38" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A38,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>4.6699999999997671E-4</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A38,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>-3.1303333333333329E-2</v>
       </c>
       <c r="G38" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A38,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A38,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H38" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A38,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A38,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I38" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A38)</f>
-        <v>-2.8000000000028002E-5</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A38)</f>
+        <v>-6.4641000000000004E-2</v>
       </c>
       <c r="J38" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A38)</f>
-        <v>9.3299999999996164E-4</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A38)</f>
+        <v>-9.099999999999997E-3</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A39,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>1.1037333333333324E-2</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A39,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>7.7336666666666942E-3</v>
       </c>
       <c r="G39" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A39,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A39,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H39" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A39,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A39,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I39" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A39)</f>
-        <v>5.9139999999999748E-3</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A39)</f>
+        <v>-1.2079999999999869E-3</v>
       </c>
       <c r="J39" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A39)</f>
-        <v>1.649299999999998E-2</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A39)</f>
+        <v>2.4136000000000046E-2</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>148</v>
@@ -3113,91 +3164,91 @@
     </row>
     <row r="40" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="F40" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A40,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>-2.3186666666666724E-3</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A40,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>4.6699999999997671E-4</v>
       </c>
       <c r="G40" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A40,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A40,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H40" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A40,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A40,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I40" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A40)</f>
-        <v>-5.6530000000000191E-3</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A40)</f>
+        <v>-2.8000000000028002E-5</v>
       </c>
       <c r="J40" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A40)</f>
-        <v>0</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A40)</f>
+        <v>9.3299999999996164E-4</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F41" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A41,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>-1.0570333333333348E-2</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A41,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>1.1037333333333324E-2</v>
       </c>
       <c r="G41" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A41,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A41,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H41" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A41,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A41,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I41" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A41)</f>
-        <v>-1.5560000000000018E-2</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A41)</f>
+        <v>5.9139999999999748E-3</v>
       </c>
       <c r="J41" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A41)</f>
-        <v>-5.4179999999999784E-3</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A41)</f>
+        <v>1.649299999999998E-2</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>148</v>
@@ -3205,105 +3256,197 @@
     </row>
     <row r="42" spans="1:13" ht="28" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>205</v>
+        <v>24</v>
       </c>
       <c r="F42" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A42,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>-4.2633333333334339E-4</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A42,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>-2.3186666666666724E-3</v>
       </c>
       <c r="G42" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A42,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A42,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H42" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A42,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A42,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I42" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A42)</f>
-        <v>-8.0900000000000416E-4</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A42)</f>
+        <v>-5.6530000000000191E-3</v>
       </c>
       <c r="J42" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A42)</f>
-        <v>-1.2000000000012001E-5</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A42)</f>
+        <v>0</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="42" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F43" s="3">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43,'Chi tiết'!$F$2:$F$331,"r2"),"")</f>
-        <v>8.4799999999997844E-4</v>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A43,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>-1.0570333333333348E-2</v>
       </c>
       <c r="G43" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43,'Chi tiết'!$F$2:$F$331,"areaUnderROC"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A43,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
         <v/>
       </c>
       <c r="H43" s="3" t="str">
-        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43,'Chi tiết'!$F$2:$F$331,"areaUnderPR"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A43,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
         <v/>
       </c>
       <c r="I43" s="3">
-        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43)</f>
-        <v>-2.1300000000001873E-4</v>
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A43)</f>
+        <v>-1.5560000000000018E-2</v>
       </c>
       <c r="J43" s="3">
-        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$331,'Chi tiết'!$A$2:$A$331,A43)</f>
-        <v>2.4819999999999842E-3</v>
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A43)</f>
+        <v>-5.4179999999999784E-3</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>148</v>
       </c>
     </row>
+    <row r="44" spans="1:13" ht="28" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F44" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A44,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>-4.2633333333334339E-4</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A44,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="3" t="str">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A44,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="3">
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A44)</f>
+        <v>-8.0900000000000416E-4</v>
+      </c>
+      <c r="J44" s="3">
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A44)</f>
+        <v>-1.2000000000012001E-5</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="42" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A45,'Chi tiết'!$F$2:$F$349,"r2"),"")</f>
+        <v>8.4799999999997844E-4</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A45,'Chi tiết'!$F$2:$F$349,"areaUnderROC"),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="3" t="str">
+        <f>IFERROR(AVERAGEIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A45,'Chi tiết'!$F$2:$F$349,"areaUnderPR"),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="3">
+        <f>_xlfn.MINIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A45)</f>
+        <v>-2.1300000000001873E-4</v>
+      </c>
+      <c r="J45" s="3">
+        <f>_xlfn.MAXIFS('Chi tiết'!$I$2:$I$349,'Chi tiết'!$A$2:$A$349,A45)</f>
+        <v>2.4819999999999842E-3</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M43" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M45" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I331"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3319,28 +3462,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -3351,16 +3494,16 @@
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G2" s="4">
         <v>1.8089999999999998E-2</v>
@@ -3381,16 +3524,16 @@
         <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G3" s="4">
         <v>1.6056000000000001E-2</v>
@@ -3411,16 +3554,16 @@
         <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G4" s="4">
         <v>5.4999999999999997E-3</v>
@@ -3441,16 +3584,16 @@
         <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G5" s="4">
         <v>0.63741999999999999</v>
@@ -3471,16 +3614,16 @@
         <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G6" s="4">
         <v>0.17575099999999999</v>
@@ -3501,16 +3644,16 @@
         <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G7" s="4">
         <v>0.63796600000000003</v>
@@ -3531,16 +3674,16 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G8" s="4">
         <v>0.16984199999999999</v>
@@ -3561,16 +3704,16 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G9" s="4">
         <v>0.65610599999999997</v>
@@ -3591,16 +3734,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G10" s="4">
         <v>0.18690200000000001</v>
@@ -3621,16 +3764,16 @@
         <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G11" s="4">
         <v>1.8089999999999998E-2</v>
@@ -3651,16 +3794,16 @@
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G12" s="4">
         <v>1.6056000000000001E-2</v>
@@ -3681,16 +3824,16 @@
         <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G13" s="4">
         <v>5.4999999999999997E-3</v>
@@ -3711,16 +3854,16 @@
         <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G14" s="4">
         <v>0.63741999999999999</v>
@@ -3741,16 +3884,16 @@
         <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G15" s="4">
         <v>0.17575099999999999</v>
@@ -3771,16 +3914,16 @@
         <v>26</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G16" s="4">
         <v>0.63796600000000003</v>
@@ -3801,16 +3944,16 @@
         <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G17" s="4">
         <v>0.16984199999999999</v>
@@ -3831,16 +3974,16 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G18" s="4">
         <v>0.65610599999999997</v>
@@ -3861,16 +4004,16 @@
         <v>26</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G19" s="4">
         <v>0.18690200000000001</v>
@@ -3897,10 +4040,10 @@
         <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G20" s="4">
         <v>2.5191999999999999E-2</v>
@@ -3927,10 +4070,10 @@
         <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G21" s="4">
         <v>5.4732999999999997E-2</v>
@@ -3957,10 +4100,10 @@
         <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G22" s="4">
         <v>5.5019999999999999E-2</v>
@@ -3987,10 +4130,10 @@
         <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G23" s="4">
         <v>0.64579699999999995</v>
@@ -4017,10 +4160,10 @@
         <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G24" s="4">
         <v>0.18444099999999999</v>
@@ -4047,10 +4190,10 @@
         <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G25" s="4">
         <v>0.67225000000000001</v>
@@ -4077,10 +4220,10 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G26" s="4">
         <v>0.248747</v>
@@ -4107,10 +4250,10 @@
         <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G27" s="4">
         <v>0.68498099999999995</v>
@@ -4137,10 +4280,10 @@
         <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G28" s="4">
         <v>0.26935999999999999</v>
@@ -4167,10 +4310,10 @@
         <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G29" s="4">
         <v>0.20142399999999999</v>
@@ -4197,10 +4340,10 @@
         <v>37</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G30" s="4">
         <v>0.26522499999999999</v>
@@ -4227,10 +4370,10 @@
         <v>37</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G31" s="4">
         <v>0.25540499999999999</v>
@@ -4257,10 +4400,10 @@
         <v>37</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G32" s="4">
         <v>0.77444199999999996</v>
@@ -4287,10 +4430,10 @@
         <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G33" s="4">
         <v>0.455822</v>
@@ -4317,10 +4460,10 @@
         <v>37</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G34" s="4">
         <v>0.79982699999999995</v>
@@ -4347,10 +4490,10 @@
         <v>37</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G35" s="4">
         <v>0.51657500000000001</v>
@@ -4377,10 +4520,10 @@
         <v>37</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G36" s="4">
         <v>0.81671899999999997</v>
@@ -4407,10 +4550,10 @@
         <v>37</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G37" s="4">
         <v>0.57144899999999998</v>
@@ -4437,10 +4580,10 @@
         <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G38" s="4">
         <v>0.266625</v>
@@ -4467,10 +4610,10 @@
         <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G39" s="4">
         <v>0.31279600000000002</v>
@@ -4497,10 +4640,10 @@
         <v>43</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G40" s="4">
         <v>0.311164</v>
@@ -4527,10 +4670,10 @@
         <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G41" s="4">
         <v>0.80227199999999999</v>
@@ -4557,10 +4700,10 @@
         <v>43</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G42" s="4">
         <v>0.52499899999999999</v>
@@ -4587,10 +4730,10 @@
         <v>43</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G43" s="4">
         <v>0.83535199999999998</v>
@@ -4617,10 +4760,10 @@
         <v>43</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G44" s="4">
         <v>0.61062700000000003</v>
@@ -4647,10 +4790,10 @@
         <v>43</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G45" s="4">
         <v>0.83543599999999996</v>
@@ -4677,10 +4820,10 @@
         <v>43</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G46" s="4">
         <v>0.62279099999999998</v>
@@ -4707,10 +4850,10 @@
         <v>49</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G47" s="4">
         <v>0.266625</v>
@@ -4737,10 +4880,10 @@
         <v>49</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G48" s="4">
         <v>0.31279600000000002</v>
@@ -4767,10 +4910,10 @@
         <v>49</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G49" s="4">
         <v>0.311164</v>
@@ -4797,10 +4940,10 @@
         <v>49</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G50" s="4">
         <v>0.80227199999999999</v>
@@ -4827,10 +4970,10 @@
         <v>49</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G51" s="4">
         <v>0.52499899999999999</v>
@@ -4857,10 +5000,10 @@
         <v>49</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G52" s="4">
         <v>0.83535199999999998</v>
@@ -4887,10 +5030,10 @@
         <v>49</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G53" s="4">
         <v>0.61062700000000003</v>
@@ -4917,10 +5060,10 @@
         <v>49</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G54" s="4">
         <v>0.83543599999999996</v>
@@ -4947,10 +5090,10 @@
         <v>49</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G55" s="4">
         <v>0.62279099999999998</v>
@@ -4971,16 +5114,16 @@
         <v>54</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G56" s="4">
         <v>1.8089999999999998E-2</v>
@@ -5001,16 +5144,16 @@
         <v>54</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G57" s="4">
         <v>1.6056000000000001E-2</v>
@@ -5031,16 +5174,16 @@
         <v>54</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G58" s="4">
         <v>5.4999999999999997E-3</v>
@@ -5061,16 +5204,16 @@
         <v>54</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G59" s="4">
         <v>0.63741999999999999</v>
@@ -5091,16 +5234,16 @@
         <v>54</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G60" s="4">
         <v>0.17575099999999999</v>
@@ -5121,16 +5264,16 @@
         <v>54</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G61" s="4">
         <v>0.63796600000000003</v>
@@ -5151,16 +5294,16 @@
         <v>54</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G62" s="4">
         <v>0.16984199999999999</v>
@@ -5181,16 +5324,16 @@
         <v>54</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G63" s="4">
         <v>0.65610599999999997</v>
@@ -5211,16 +5354,16 @@
         <v>54</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G64" s="4">
         <v>0.18690200000000001</v>
@@ -5247,10 +5390,10 @@
         <v>58</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G65" s="4">
         <v>2.5191999999999999E-2</v>
@@ -5277,10 +5420,10 @@
         <v>58</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G66" s="4">
         <v>5.4732999999999997E-2</v>
@@ -5307,10 +5450,10 @@
         <v>58</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G67" s="4">
         <v>5.5019999999999999E-2</v>
@@ -5337,10 +5480,10 @@
         <v>58</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G68" s="4">
         <v>0.64579699999999995</v>
@@ -5367,10 +5510,10 @@
         <v>58</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G69" s="4">
         <v>0.18444099999999999</v>
@@ -5397,10 +5540,10 @@
         <v>58</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G70" s="4">
         <v>0.67225000000000001</v>
@@ -5427,10 +5570,10 @@
         <v>58</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G71" s="4">
         <v>0.248747</v>
@@ -5457,10 +5600,10 @@
         <v>58</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G72" s="4">
         <v>0.68498099999999995</v>
@@ -5487,10 +5630,10 @@
         <v>58</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G73" s="4">
         <v>0.26935999999999999</v>
@@ -5517,10 +5660,10 @@
         <v>61</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G74" s="4">
         <v>0.266625</v>
@@ -5547,10 +5690,10 @@
         <v>61</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G75" s="4">
         <v>0.31279600000000002</v>
@@ -5577,10 +5720,10 @@
         <v>61</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G76" s="4">
         <v>0.311164</v>
@@ -5607,10 +5750,10 @@
         <v>61</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G77" s="4">
         <v>0.80227199999999999</v>
@@ -5637,10 +5780,10 @@
         <v>61</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G78" s="4">
         <v>0.52499899999999999</v>
@@ -5667,10 +5810,10 @@
         <v>61</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G79" s="4">
         <v>0.83535199999999998</v>
@@ -5697,10 +5840,10 @@
         <v>61</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G80" s="4">
         <v>0.61062700000000003</v>
@@ -5727,10 +5870,10 @@
         <v>61</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G81" s="4">
         <v>0.83543599999999996</v>
@@ -5757,10 +5900,10 @@
         <v>61</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G82" s="4">
         <v>0.62279099999999998</v>
@@ -5781,16 +5924,16 @@
         <v>66</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G83" s="4">
         <v>0.265982</v>
@@ -5811,16 +5954,16 @@
         <v>66</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G84" s="4">
         <v>0.31615300000000002</v>
@@ -5841,16 +5984,16 @@
         <v>66</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G85" s="4">
         <v>0.31152299999999999</v>
@@ -5871,16 +6014,16 @@
         <v>66</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G86" s="4">
         <v>0.79934400000000005</v>
@@ -5901,16 +6044,16 @@
         <v>66</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G87" s="4">
         <v>0.52996799999999999</v>
@@ -5931,16 +6074,16 @@
         <v>66</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G88" s="4">
         <v>0.82991999999999999</v>
@@ -5961,16 +6104,16 @@
         <v>66</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G89" s="4">
         <v>0.609954</v>
@@ -5991,16 +6134,16 @@
         <v>66</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G90" s="4">
         <v>0.83391700000000002</v>
@@ -6021,16 +6164,16 @@
         <v>66</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G91" s="4">
         <v>0.619668</v>
@@ -6051,16 +6194,16 @@
         <v>71</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G92" s="4">
         <v>0.265982</v>
@@ -6081,16 +6224,16 @@
         <v>71</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G93" s="4">
         <v>0.31615300000000002</v>
@@ -6111,16 +6254,16 @@
         <v>71</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G94" s="4">
         <v>0.31152299999999999</v>
@@ -6141,16 +6284,16 @@
         <v>71</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G95" s="4">
         <v>0.79934400000000005</v>
@@ -6171,16 +6314,16 @@
         <v>71</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G96" s="4">
         <v>0.52996799999999999</v>
@@ -6201,16 +6344,16 @@
         <v>71</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G97" s="4">
         <v>0.82991999999999999</v>
@@ -6231,16 +6374,16 @@
         <v>71</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G98" s="4">
         <v>0.609954</v>
@@ -6261,16 +6404,16 @@
         <v>71</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G99" s="4">
         <v>0.83391700000000002</v>
@@ -6291,16 +6434,16 @@
         <v>71</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G100" s="4">
         <v>0.619668</v>
@@ -6321,16 +6464,16 @@
         <v>77</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G101" s="4">
         <v>0.265982</v>
@@ -6351,16 +6494,16 @@
         <v>77</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G102" s="4">
         <v>0.31615300000000002</v>
@@ -6381,16 +6524,16 @@
         <v>77</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G103" s="4">
         <v>0.31152299999999999</v>
@@ -6411,16 +6554,16 @@
         <v>77</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G104" s="4">
         <v>0.79934400000000005</v>
@@ -6441,16 +6584,16 @@
         <v>77</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G105" s="4">
         <v>0.52996799999999999</v>
@@ -6471,16 +6614,16 @@
         <v>77</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G106" s="4">
         <v>0.82991999999999999</v>
@@ -6501,16 +6644,16 @@
         <v>77</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G107" s="4">
         <v>0.609954</v>
@@ -6531,16 +6674,16 @@
         <v>77</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G108" s="4">
         <v>0.83391700000000002</v>
@@ -6561,16 +6704,16 @@
         <v>77</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>77</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G109" s="4">
         <v>0.619668</v>
@@ -6594,13 +6737,13 @@
         <v>82</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G110" s="4">
         <v>1.9293999999999999E-2</v>
@@ -6624,13 +6767,13 @@
         <v>82</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G111" s="4">
         <v>1.8152000000000001E-2</v>
@@ -6654,13 +6797,13 @@
         <v>82</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G112" s="4">
         <v>2.6574E-2</v>
@@ -6684,13 +6827,13 @@
         <v>82</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G113" s="4">
         <v>0.63682000000000005</v>
@@ -6714,13 +6857,13 @@
         <v>82</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G114" s="4">
         <v>0.17542099999999999</v>
@@ -6744,13 +6887,13 @@
         <v>82</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G115" s="4">
         <v>0.64645300000000006</v>
@@ -6774,13 +6917,13 @@
         <v>82</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G116" s="4">
         <v>0.17816699999999999</v>
@@ -6804,13 +6947,13 @@
         <v>82</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G117" s="4">
         <v>0.66634899999999997</v>
@@ -6834,13 +6977,13 @@
         <v>82</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G118" s="4">
         <v>0.19419500000000001</v>
@@ -6861,16 +7004,16 @@
         <v>88</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G119" s="4">
         <v>0.245472</v>
@@ -6891,16 +7034,16 @@
         <v>88</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G120" s="4">
         <v>0.282416</v>
@@ -6921,16 +7064,16 @@
         <v>88</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G121" s="4">
         <v>0.28014600000000001</v>
@@ -6951,16 +7094,16 @@
         <v>88</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G122" s="4">
         <v>0.80170399999999997</v>
@@ -6981,16 +7124,16 @@
         <v>88</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G123" s="4">
         <v>0.553122</v>
@@ -7011,16 +7154,16 @@
         <v>88</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G124" s="4">
         <v>0.82854399999999995</v>
@@ -7041,16 +7184,16 @@
         <v>88</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G125" s="4">
         <v>0.61828399999999994</v>
@@ -7071,16 +7214,16 @@
         <v>88</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G126" s="4">
         <v>0.83161499999999999</v>
@@ -7101,16 +7244,16 @@
         <v>88</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G127" s="4">
         <v>0.63358099999999995</v>
@@ -7131,16 +7274,16 @@
         <v>94</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G128" s="4">
         <v>0.245472</v>
@@ -7161,16 +7304,16 @@
         <v>94</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G129" s="4">
         <v>0.282416</v>
@@ -7191,16 +7334,16 @@
         <v>94</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G130" s="4">
         <v>0.28014600000000001</v>
@@ -7221,16 +7364,16 @@
         <v>94</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G131" s="4">
         <v>0.80169299999999999</v>
@@ -7251,16 +7394,16 @@
         <v>94</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G132" s="4">
         <v>0.55311999999999995</v>
@@ -7281,16 +7424,16 @@
         <v>94</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G133" s="4">
         <v>0.82854399999999995</v>
@@ -7311,16 +7454,16 @@
         <v>94</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G134" s="4">
         <v>0.61828399999999994</v>
@@ -7341,16 +7484,16 @@
         <v>94</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G135" s="4">
         <v>0.83161499999999999</v>
@@ -7371,16 +7514,16 @@
         <v>94</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G136" s="4">
         <v>0.63358099999999995</v>
@@ -7401,16 +7544,16 @@
         <v>94</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G137" s="4">
         <v>0.245472</v>
@@ -7431,16 +7574,16 @@
         <v>94</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G138" s="4">
         <v>0.282416</v>
@@ -7461,16 +7604,16 @@
         <v>94</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G139" s="4">
         <v>0.28014600000000001</v>
@@ -7491,16 +7634,16 @@
         <v>94</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G140" s="4">
         <v>0.80169299999999999</v>
@@ -7521,16 +7664,16 @@
         <v>94</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G141" s="4">
         <v>0.55311999999999995</v>
@@ -7551,16 +7694,16 @@
         <v>94</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G142" s="4">
         <v>0.82854399999999995</v>
@@ -7581,16 +7724,16 @@
         <v>94</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G143" s="4">
         <v>0.61828399999999994</v>
@@ -7611,16 +7754,16 @@
         <v>94</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G144" s="4">
         <v>0.83161499999999999</v>
@@ -7641,16 +7784,16 @@
         <v>94</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G145" s="4">
         <v>0.63358099999999995</v>
@@ -7671,16 +7814,16 @@
         <v>104</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D146" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="F146" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G146" s="4">
         <v>0.245472</v>
@@ -7701,16 +7844,16 @@
         <v>104</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G147" s="4">
         <v>0.282416</v>
@@ -7731,16 +7874,16 @@
         <v>104</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G148" s="4">
         <v>0.28014600000000001</v>
@@ -7761,16 +7904,16 @@
         <v>104</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G149" s="4">
         <v>0.80169999999999997</v>
@@ -7791,16 +7934,16 @@
         <v>104</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G150" s="4">
         <v>0.553118</v>
@@ -7821,16 +7964,16 @@
         <v>104</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G151" s="4">
         <v>0.82854399999999995</v>
@@ -7851,16 +7994,16 @@
         <v>104</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G152" s="4">
         <v>0.61828399999999994</v>
@@ -7881,16 +8024,16 @@
         <v>104</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G153" s="4">
         <v>0.83161499999999999</v>
@@ -7911,16 +8054,16 @@
         <v>104</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G154" s="4">
         <v>0.63358099999999995</v>
@@ -7941,16 +8084,16 @@
         <v>104</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D155" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="G155" s="4">
         <v>0.245472</v>
@@ -7971,16 +8114,16 @@
         <v>104</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D156" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="G156" s="4">
         <v>0.282416</v>
@@ -8001,16 +8144,16 @@
         <v>104</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D157" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="G157" s="4">
         <v>0.28014600000000001</v>
@@ -8031,16 +8174,16 @@
         <v>104</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G158" s="4">
         <v>0.80169999999999997</v>
@@ -8061,16 +8204,16 @@
         <v>104</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G159" s="4">
         <v>0.553118</v>
@@ -8091,16 +8234,16 @@
         <v>104</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G160" s="4">
         <v>0.82854399999999995</v>
@@ -8121,16 +8264,16 @@
         <v>104</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G161" s="4">
         <v>0.61828399999999994</v>
@@ -8151,16 +8294,16 @@
         <v>104</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G162" s="4">
         <v>0.83161499999999999</v>
@@ -8181,16 +8324,16 @@
         <v>104</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G163" s="4">
         <v>0.63358099999999995</v>
@@ -8211,16 +8354,16 @@
         <v>114</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G164" s="4">
         <v>0.245472</v>
@@ -8241,16 +8384,16 @@
         <v>114</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D165" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="F165" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G165" s="4">
         <v>0.282416</v>
@@ -8271,16 +8414,16 @@
         <v>114</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G166" s="4">
         <v>0.28014600000000001</v>
@@ -8301,16 +8444,16 @@
         <v>114</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G167" s="4">
         <v>0.80169800000000002</v>
@@ -8331,16 +8474,16 @@
         <v>114</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G168" s="4">
         <v>0.55312099999999997</v>
@@ -8361,16 +8504,16 @@
         <v>114</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G169" s="4">
         <v>0.82854399999999995</v>
@@ -8391,16 +8534,16 @@
         <v>114</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G170" s="4">
         <v>0.61828399999999994</v>
@@ -8421,16 +8564,16 @@
         <v>114</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G171" s="4">
         <v>0.83161499999999999</v>
@@ -8451,16 +8594,16 @@
         <v>114</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G172" s="4">
         <v>0.63358099999999995</v>
@@ -8481,16 +8624,16 @@
         <v>120</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G173" s="4">
         <v>0.245472</v>
@@ -8511,16 +8654,16 @@
         <v>120</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G174" s="4">
         <v>0.282416</v>
@@ -8541,16 +8684,16 @@
         <v>120</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="F175" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G175" s="4">
         <v>0.28014600000000001</v>
@@ -8571,16 +8714,16 @@
         <v>120</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G176" s="4">
         <v>0.80169400000000002</v>
@@ -8601,16 +8744,16 @@
         <v>120</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G177" s="4">
         <v>0.55312399999999995</v>
@@ -8631,16 +8774,16 @@
         <v>120</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G178" s="4">
         <v>0.82854399999999995</v>
@@ -8661,16 +8804,16 @@
         <v>120</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G179" s="4">
         <v>0.61828399999999994</v>
@@ -8691,16 +8834,16 @@
         <v>120</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G180" s="4">
         <v>0.83161499999999999</v>
@@ -8721,16 +8864,16 @@
         <v>120</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G181" s="4">
         <v>0.63358099999999995</v>
@@ -8751,16 +8894,16 @@
         <v>120</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G182" s="4">
         <v>0.245472</v>
@@ -8781,16 +8924,16 @@
         <v>120</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G183" s="4">
         <v>0.282416</v>
@@ -8811,16 +8954,16 @@
         <v>120</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G184" s="4">
         <v>0.28014600000000001</v>
@@ -8841,16 +8984,16 @@
         <v>120</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E185" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G185" s="4">
         <v>0.80169400000000002</v>
@@ -8871,16 +9014,16 @@
         <v>120</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E186" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="F186" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G186" s="4">
         <v>0.55312399999999995</v>
@@ -8901,16 +9044,16 @@
         <v>120</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G187" s="4">
         <v>0.82854399999999995</v>
@@ -8931,16 +9074,16 @@
         <v>120</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G188" s="4">
         <v>0.61828399999999994</v>
@@ -8961,16 +9104,16 @@
         <v>120</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G189" s="4">
         <v>0.83161499999999999</v>
@@ -8991,16 +9134,16 @@
         <v>120</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G190" s="4">
         <v>0.63358099999999995</v>
@@ -9021,16 +9164,16 @@
         <v>131</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G191" s="4">
         <v>0.245472</v>
@@ -9051,16 +9194,16 @@
         <v>131</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G192" s="4">
         <v>0.282416</v>
@@ -9081,16 +9224,16 @@
         <v>131</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G193" s="4">
         <v>0.28014600000000001</v>
@@ -9111,16 +9254,16 @@
         <v>131</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="G194" s="4">
         <v>0.80170200000000003</v>
@@ -9141,16 +9284,16 @@
         <v>131</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G195" s="4">
         <v>0.55312099999999997</v>
@@ -9171,16 +9314,16 @@
         <v>131</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D196" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="G196" s="4">
         <v>0.82854399999999995</v>
@@ -9201,16 +9344,16 @@
         <v>131</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G197" s="4">
         <v>0.61828399999999994</v>
@@ -9231,16 +9374,16 @@
         <v>131</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D198" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="G198" s="4">
         <v>0.83161499999999999</v>
@@ -9261,16 +9404,16 @@
         <v>131</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G199" s="4">
         <v>0.63358099999999995</v>
@@ -9291,16 +9434,16 @@
         <v>131</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G200" s="4">
         <v>0.245472</v>
@@ -9321,16 +9464,16 @@
         <v>131</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G201" s="4">
         <v>0.282416</v>
@@ -9351,16 +9494,16 @@
         <v>131</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G202" s="4">
         <v>0.28014600000000001</v>
@@ -9381,16 +9524,16 @@
         <v>131</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G203" s="4">
         <v>0.80170200000000003</v>
@@ -9411,16 +9554,16 @@
         <v>131</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G204" s="4">
         <v>0.55312099999999997</v>
@@ -9441,16 +9584,16 @@
         <v>131</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G205" s="4">
         <v>0.82854399999999995</v>
@@ -9471,16 +9614,16 @@
         <v>131</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G206" s="4">
         <v>0.61828399999999994</v>
@@ -9501,16 +9644,16 @@
         <v>131</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G207" s="4">
         <v>0.83161499999999999</v>
@@ -9531,16 +9674,16 @@
         <v>131</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="G208" s="4">
         <v>0.63358099999999995</v>
@@ -9561,16 +9704,16 @@
         <v>131</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G209" s="4">
         <v>0.245472</v>
@@ -9591,16 +9734,16 @@
         <v>131</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G210" s="4">
         <v>0.282416</v>
@@ -9621,16 +9764,16 @@
         <v>131</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G211" s="4">
         <v>0.28014600000000001</v>
@@ -9651,16 +9794,16 @@
         <v>131</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G212" s="4">
         <v>0.80170200000000003</v>
@@ -9681,16 +9824,16 @@
         <v>131</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G213" s="4">
         <v>0.55312099999999997</v>
@@ -9711,16 +9854,16 @@
         <v>131</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E214" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="F214" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G214" s="4">
         <v>0.82854399999999995</v>
@@ -9741,16 +9884,16 @@
         <v>131</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D215" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E215" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="F215" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G215" s="4">
         <v>0.61828399999999994</v>
@@ -9771,16 +9914,16 @@
         <v>131</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G216" s="4">
         <v>0.83161499999999999</v>
@@ -9801,16 +9944,16 @@
         <v>131</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G217" s="4">
         <v>0.63358099999999995</v>
@@ -9831,16 +9974,16 @@
         <v>131</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G218" s="4">
         <v>0.245472</v>
@@ -9861,16 +10004,16 @@
         <v>131</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G219" s="4">
         <v>0.282416</v>
@@ -9891,16 +10034,16 @@
         <v>131</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G220" s="4">
         <v>0.28014600000000001</v>
@@ -9921,16 +10064,16 @@
         <v>131</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G221" s="4">
         <v>0.80170200000000003</v>
@@ -9951,16 +10094,16 @@
         <v>131</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G222" s="4">
         <v>0.55312099999999997</v>
@@ -9981,16 +10124,16 @@
         <v>131</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G223" s="4">
         <v>0.82854399999999995</v>
@@ -10011,16 +10154,16 @@
         <v>131</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G224" s="4">
         <v>0.61828399999999994</v>
@@ -10041,16 +10184,16 @@
         <v>131</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D225" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G225" s="4">
         <v>0.83161499999999999</v>
@@ -10071,16 +10214,16 @@
         <v>131</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D226" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F226" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G226" s="4">
         <v>0.63358099999999995</v>
@@ -10101,16 +10244,16 @@
         <v>147</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D227" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E227" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="F227" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G227" s="4">
         <v>0.31461099999999997</v>
@@ -10131,16 +10274,16 @@
         <v>147</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G228" s="4">
         <v>0.36653999999999998</v>
@@ -10161,16 +10304,16 @@
         <v>147</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G229" s="4">
         <v>0.34986600000000001</v>
@@ -10191,16 +10334,16 @@
         <v>147</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G230" s="4">
         <v>0.79687799999999998</v>
@@ -10221,16 +10364,16 @@
         <v>147</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G231" s="4">
         <v>0.56104900000000002</v>
@@ -10251,16 +10394,16 @@
         <v>147</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G232" s="4">
         <v>0.82152199999999997</v>
@@ -10281,16 +10424,16 @@
         <v>147</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G233" s="4">
         <v>0.61744399999999999</v>
@@ -10311,16 +10454,16 @@
         <v>147</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G234" s="4">
         <v>0.82388600000000001</v>
@@ -10341,16 +10484,16 @@
         <v>147</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G235" s="4">
         <v>0.63169399999999998</v>
@@ -10371,16 +10514,16 @@
         <v>151</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G236" s="4">
         <v>0.3599</v>
@@ -10401,16 +10544,16 @@
         <v>151</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G237" s="4">
         <v>0.35105799999999998</v>
@@ -10431,16 +10574,16 @@
         <v>151</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G238" s="4">
         <v>0.32555699999999999</v>
@@ -10461,16 +10604,16 @@
         <v>151</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G239" s="4">
         <v>0.81636699999999995</v>
@@ -10491,16 +10634,16 @@
         <v>151</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G240" s="4">
         <v>0.55715800000000004</v>
@@ -10521,16 +10664,16 @@
         <v>151</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G241" s="4">
         <v>0.83724399999999999</v>
@@ -10551,16 +10694,16 @@
         <v>151</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G242" s="4">
         <v>0.61881200000000003</v>
@@ -10581,16 +10724,16 @@
         <v>151</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G243" s="4">
         <v>0.83833299999999999</v>
@@ -10611,16 +10754,16 @@
         <v>151</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G244" s="4">
         <v>0.63338399999999995</v>
@@ -10641,16 +10784,16 @@
         <v>154</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G245" s="4">
         <v>0.24327699999999999</v>
@@ -10671,16 +10814,16 @@
         <v>154</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G246" s="4">
         <v>0.34002199999999999</v>
@@ -10701,16 +10844,16 @@
         <v>154</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G247" s="4">
         <v>0.33022400000000002</v>
@@ -10731,16 +10874,16 @@
         <v>154</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G248" s="4">
         <v>0.79859000000000002</v>
@@ -10761,16 +10904,16 @@
         <v>154</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G249" s="4">
         <v>0.51651000000000002</v>
@@ -10791,16 +10934,16 @@
         <v>154</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G250" s="4">
         <v>0.83457499999999996</v>
@@ -10821,16 +10964,16 @@
         <v>154</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G251" s="4">
         <v>0.62294300000000002</v>
@@ -10851,16 +10994,16 @@
         <v>154</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G252" s="4">
         <v>0.83736999999999995</v>
@@ -10881,16 +11024,16 @@
         <v>154</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G253" s="4">
         <v>0.63007999999999997</v>
@@ -10911,16 +11054,16 @@
         <v>147</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G254" s="4">
         <v>0.31461099999999997</v>
@@ -10941,16 +11084,16 @@
         <v>147</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G255" s="4">
         <v>0.36653999999999998</v>
@@ -10971,16 +11114,16 @@
         <v>147</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="F256" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G256" s="4">
         <v>0.34986600000000001</v>
@@ -11001,16 +11144,16 @@
         <v>147</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G257" s="4">
         <v>0.79687799999999998</v>
@@ -11031,16 +11174,16 @@
         <v>147</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G258" s="4">
         <v>0.56104900000000002</v>
@@ -11061,16 +11204,16 @@
         <v>147</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G259" s="4">
         <v>0.82152199999999997</v>
@@ -11091,16 +11234,16 @@
         <v>147</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G260" s="4">
         <v>0.61744399999999999</v>
@@ -11121,16 +11264,16 @@
         <v>147</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G261" s="4">
         <v>0.82388600000000001</v>
@@ -11151,16 +11294,16 @@
         <v>147</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G262" s="4">
         <v>0.63169399999999998</v>
@@ -11181,16 +11324,16 @@
         <v>151</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G263" s="4">
         <v>0.3599</v>
@@ -11211,16 +11354,16 @@
         <v>151</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G264" s="4">
         <v>0.35105799999999998</v>
@@ -11241,16 +11384,16 @@
         <v>151</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G265" s="4">
         <v>0.32555699999999999</v>
@@ -11271,16 +11414,16 @@
         <v>151</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G266" s="4">
         <v>0.81636699999999995</v>
@@ -11301,16 +11444,16 @@
         <v>151</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G267" s="4">
         <v>0.55715800000000004</v>
@@ -11331,16 +11474,16 @@
         <v>151</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G268" s="4">
         <v>0.83724399999999999</v>
@@ -11361,16 +11504,16 @@
         <v>151</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G269" s="4">
         <v>0.61881200000000003</v>
@@ -11391,16 +11534,16 @@
         <v>151</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G270" s="4">
         <v>0.83833299999999999</v>
@@ -11421,16 +11564,16 @@
         <v>151</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G271" s="4">
         <v>0.63338399999999995</v>
@@ -11451,16 +11594,16 @@
         <v>154</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G272" s="4">
         <v>0.24327699999999999</v>
@@ -11481,16 +11624,16 @@
         <v>154</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G273" s="4">
         <v>0.34002199999999999</v>
@@ -11511,16 +11654,16 @@
         <v>154</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G274" s="4">
         <v>0.33022400000000002</v>
@@ -11541,16 +11684,16 @@
         <v>154</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G275" s="4">
         <v>0.79859000000000002</v>
@@ -11571,16 +11714,16 @@
         <v>154</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G276" s="4">
         <v>0.51651000000000002</v>
@@ -11601,16 +11744,16 @@
         <v>154</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G277" s="4">
         <v>0.83457499999999996</v>
@@ -11631,16 +11774,16 @@
         <v>154</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G278" s="4">
         <v>0.62294300000000002</v>
@@ -11661,16 +11804,16 @@
         <v>154</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G279" s="4">
         <v>0.83736999999999995</v>
@@ -11691,16 +11834,16 @@
         <v>154</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G280" s="4">
         <v>0.63007999999999997</v>
@@ -11721,16 +11864,16 @@
         <v>147</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G281" s="4">
         <v>0.31461099999999997</v>
@@ -11751,16 +11894,16 @@
         <v>147</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G282" s="4">
         <v>0.36653999999999998</v>
@@ -11781,16 +11924,16 @@
         <v>147</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G283" s="4">
         <v>0.34986600000000001</v>
@@ -11811,16 +11954,16 @@
         <v>147</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G284" s="4">
         <v>0.79687799999999998</v>
@@ -11841,16 +11984,16 @@
         <v>147</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G285" s="4">
         <v>0.56104900000000002</v>
@@ -11871,16 +12014,16 @@
         <v>147</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G286" s="4">
         <v>0.82152199999999997</v>
@@ -11901,16 +12044,16 @@
         <v>147</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G287" s="4">
         <v>0.61744399999999999</v>
@@ -11931,16 +12074,16 @@
         <v>147</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G288" s="4">
         <v>0.82388600000000001</v>
@@ -11961,16 +12104,16 @@
         <v>147</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G289" s="4">
         <v>0.63169399999999998</v>
@@ -11991,16 +12134,16 @@
         <v>170</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G290" s="4">
         <v>0.245472</v>
@@ -12021,16 +12164,16 @@
         <v>170</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G291" s="4">
         <v>0.282416</v>
@@ -12051,16 +12194,16 @@
         <v>170</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G292" s="4">
         <v>0.28014600000000001</v>
@@ -12081,16 +12224,16 @@
         <v>170</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G293" s="4">
         <v>0.80170600000000003</v>
@@ -12111,16 +12254,16 @@
         <v>170</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G294" s="4">
         <v>0.55311699999999997</v>
@@ -12141,16 +12284,16 @@
         <v>170</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G295" s="4">
         <v>0.82854399999999995</v>
@@ -12171,16 +12314,16 @@
         <v>170</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G296" s="4">
         <v>0.61828399999999994</v>
@@ -12201,16 +12344,16 @@
         <v>170</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G297" s="4">
         <v>0.83161499999999999</v>
@@ -12231,16 +12374,16 @@
         <v>170</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G298" s="4">
         <v>0.63358099999999995</v>
@@ -12261,16 +12404,16 @@
         <v>170</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G299" s="4">
         <v>0.245472</v>
@@ -12291,16 +12434,16 @@
         <v>170</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G300" s="4">
         <v>0.282416</v>
@@ -12321,16 +12464,16 @@
         <v>170</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G301" s="4">
         <v>0.28014600000000001</v>
@@ -12351,16 +12494,16 @@
         <v>170</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G302" s="4">
         <v>0.80170600000000003</v>
@@ -12381,16 +12524,16 @@
         <v>170</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G303" s="4">
         <v>0.55311699999999997</v>
@@ -12411,16 +12554,16 @@
         <v>170</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G304" s="4">
         <v>0.82854399999999995</v>
@@ -12441,16 +12584,16 @@
         <v>170</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G305" s="4">
         <v>0.61828399999999994</v>
@@ -12471,16 +12614,16 @@
         <v>170</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G306" s="4">
         <v>0.83161499999999999</v>
@@ -12501,16 +12644,16 @@
         <v>170</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G307" s="4">
         <v>0.63358099999999995</v>
@@ -12528,29 +12671,29 @@
         <v>175</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G308" s="4">
-        <v>0.44441799999999998</v>
+        <v>0.31276100000000001</v>
       </c>
       <c r="H308" s="4">
-        <v>0.37977699999999998</v>
+        <v>0.319357</v>
       </c>
       <c r="I308" s="3">
         <f t="shared" si="4"/>
-        <v>-6.4641000000000004E-2</v>
+        <v>6.5959999999999908E-3</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.35">
@@ -12558,29 +12701,29 @@
         <v>175</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G309" s="4">
-        <v>0.40514899999999998</v>
+        <v>0.36671500000000001</v>
       </c>
       <c r="H309" s="4">
-        <v>0.39604899999999998</v>
+        <v>0.36513600000000002</v>
       </c>
       <c r="I309" s="3">
         <f t="shared" si="4"/>
-        <v>-9.099999999999997E-3</v>
+        <v>-1.5789999999999971E-3</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.35">
@@ -12588,663 +12731,1203 @@
         <v>175</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G310" s="4">
-        <v>0.42920700000000001</v>
+        <v>0.34456500000000001</v>
       </c>
       <c r="H310" s="4">
-        <v>0.40903800000000001</v>
+        <v>0.36249100000000001</v>
       </c>
       <c r="I310" s="3">
         <f t="shared" si="4"/>
-        <v>-2.0168999999999992E-2</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+        <v>1.7925999999999997E-2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B311" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C311" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G311" s="4">
-        <v>0.44441799999999998</v>
+        <v>0.79774100000000003</v>
       </c>
       <c r="H311" s="4">
-        <v>0.46855400000000003</v>
+        <v>0.80204600000000004</v>
       </c>
       <c r="I311" s="3">
         <f t="shared" si="4"/>
-        <v>2.4136000000000046E-2</v>
+        <v>4.3050000000000033E-3</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C312" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G312" s="4">
-        <v>0.40514899999999998</v>
+        <v>0.56656399999999996</v>
       </c>
       <c r="H312" s="4">
-        <v>0.405422</v>
+        <v>0.59527399999999997</v>
       </c>
       <c r="I312" s="3">
         <f t="shared" si="4"/>
-        <v>2.7300000000002322E-4</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+        <v>2.8710000000000013E-2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="C313" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G313" s="4">
-        <v>0.42920700000000001</v>
+        <v>0.82274999999999998</v>
       </c>
       <c r="H313" s="4">
-        <v>0.42799900000000002</v>
+        <v>0.82254000000000005</v>
       </c>
       <c r="I313" s="3">
         <f t="shared" si="4"/>
-        <v>-1.2079999999999869E-3</v>
+        <v>-2.0999999999993246E-4</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G314" s="4">
-        <v>0.46855400000000003</v>
+        <v>0.61728400000000005</v>
       </c>
       <c r="H314" s="4">
-        <v>0.46905000000000002</v>
+        <v>0.62156900000000004</v>
       </c>
       <c r="I314" s="3">
         <f t="shared" si="4"/>
-        <v>4.9599999999999644E-4</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+        <v>4.2849999999999833E-3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G315" s="4">
-        <v>0.405422</v>
+        <v>0.82588499999999998</v>
       </c>
       <c r="H315" s="4">
-        <v>0.40539399999999998</v>
+        <v>0.82549499999999998</v>
       </c>
       <c r="I315" s="3">
         <f t="shared" si="4"/>
-        <v>-2.8000000000028002E-5</v>
+        <v>-3.9000000000000146E-4</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G316" s="4">
-        <v>0.42799900000000002</v>
+        <v>0.63196699999999995</v>
       </c>
       <c r="H316" s="4">
-        <v>0.42893199999999998</v>
+        <v>0.63211099999999998</v>
       </c>
       <c r="I316" s="3">
         <f t="shared" si="4"/>
-        <v>9.3299999999996164E-4</v>
+        <v>1.4400000000003299E-4</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G317" s="4">
-        <v>0.46855400000000003</v>
+        <v>0.31276100000000001</v>
       </c>
       <c r="H317" s="4">
-        <v>0.474468</v>
+        <v>0.31733499999999998</v>
       </c>
       <c r="I317" s="3">
         <f t="shared" si="4"/>
-        <v>5.9139999999999748E-3</v>
+        <v>4.573999999999967E-3</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G318" s="4">
-        <v>0.405422</v>
+        <v>0.36671500000000001</v>
       </c>
       <c r="H318" s="4">
-        <v>0.41612700000000002</v>
+        <v>0.36951899999999999</v>
       </c>
       <c r="I318" s="3">
         <f t="shared" si="4"/>
-        <v>1.070500000000002E-2</v>
+        <v>2.8039999999999732E-3</v>
       </c>
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G319" s="4">
-        <v>0.42799900000000002</v>
+        <v>0.34456500000000001</v>
       </c>
       <c r="H319" s="4">
-        <v>0.444492</v>
+        <v>0.34456500000000001</v>
       </c>
       <c r="I319" s="3">
         <f t="shared" si="4"/>
-        <v>1.649299999999998E-2</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G320" s="4">
-        <v>0.474468</v>
+        <v>0.79774400000000001</v>
       </c>
       <c r="H320" s="4">
-        <v>0.46881499999999998</v>
+        <v>0.797736</v>
       </c>
       <c r="I320" s="3">
         <f t="shared" si="4"/>
-        <v>-5.6530000000000191E-3</v>
+        <v>-8.0000000000080007E-6</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G321" s="4">
-        <v>0.41612700000000002</v>
+        <v>0.56657199999999996</v>
       </c>
       <c r="H321" s="4">
-        <v>0.41482400000000003</v>
+        <v>0.56691999999999998</v>
       </c>
       <c r="I321" s="3">
         <f t="shared" si="4"/>
-        <v>-1.3029999999999986E-3</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+        <v>3.4800000000001496E-4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G322" s="4">
-        <v>0.444492</v>
+        <v>0.82274999999999998</v>
       </c>
       <c r="H322" s="4">
-        <v>0.444492</v>
+        <v>0.82274700000000001</v>
       </c>
       <c r="I322" s="3">
         <f t="shared" ref="I322:I385" si="5">H322-G322</f>
-        <v>0</v>
+        <v>-2.9999999999752447E-6</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G323" s="4">
-        <v>0.474468</v>
+        <v>0.61728400000000005</v>
       </c>
       <c r="H323" s="4">
-        <v>0.46905000000000002</v>
+        <v>0.617282</v>
       </c>
       <c r="I323" s="3">
         <f t="shared" si="5"/>
-        <v>-5.4179999999999784E-3</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+        <v>-2.0000000000575113E-6</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="G324" s="4">
-        <v>0.41612700000000002</v>
+        <v>0.82588499999999998</v>
       </c>
       <c r="H324" s="4">
-        <v>0.40539399999999998</v>
+        <v>0.82588300000000003</v>
       </c>
       <c r="I324" s="3">
         <f t="shared" si="5"/>
-        <v>-1.0733000000000048E-2</v>
+        <v>-1.999999999946489E-6</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G325" s="4">
-        <v>0.444492</v>
+        <v>0.63196699999999995</v>
       </c>
       <c r="H325" s="4">
-        <v>0.42893199999999998</v>
+        <v>0.63196300000000005</v>
       </c>
       <c r="I325" s="3">
         <f t="shared" si="5"/>
-        <v>-1.5560000000000018E-2</v>
+        <v>-3.9999999998929781E-6</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G326" s="4">
-        <v>0.474468</v>
+        <v>0.44441799999999998</v>
       </c>
       <c r="H326" s="4">
-        <v>0.47445599999999999</v>
+        <v>0.37977699999999998</v>
       </c>
       <c r="I326" s="3">
         <f t="shared" si="5"/>
-        <v>-1.2000000000012001E-5</v>
+        <v>-6.4641000000000004E-2</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G327" s="4">
-        <v>0.41612700000000002</v>
+        <v>0.40514899999999998</v>
       </c>
       <c r="H327" s="4">
-        <v>0.41566900000000001</v>
+        <v>0.39604899999999998</v>
       </c>
       <c r="I327" s="3">
         <f t="shared" si="5"/>
-        <v>-4.5800000000001395E-4</v>
+        <v>-9.099999999999997E-3</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G328" s="4">
-        <v>0.444492</v>
+        <v>0.42920700000000001</v>
       </c>
       <c r="H328" s="4">
-        <v>0.44368299999999999</v>
+        <v>0.40903800000000001</v>
       </c>
       <c r="I328" s="3">
         <f t="shared" si="5"/>
-        <v>-8.0900000000000416E-4</v>
+        <v>-2.0168999999999992E-2</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G329" s="4">
-        <v>0.474468</v>
+        <v>0.44441799999999998</v>
       </c>
       <c r="H329" s="4">
-        <v>0.47425499999999998</v>
+        <v>0.46855400000000003</v>
       </c>
       <c r="I329" s="3">
         <f t="shared" si="5"/>
-        <v>-2.1300000000001873E-4</v>
+        <v>2.4136000000000046E-2</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G330" s="4">
-        <v>0.41612700000000002</v>
+        <v>0.40514899999999998</v>
       </c>
       <c r="H330" s="4">
-        <v>0.41640199999999999</v>
+        <v>0.405422</v>
       </c>
       <c r="I330" s="3">
         <f t="shared" si="5"/>
-        <v>2.7499999999996971E-4</v>
+        <v>2.7300000000002322E-4</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G331" s="4">
-        <v>0.444492</v>
+        <v>0.42920700000000001</v>
       </c>
       <c r="H331" s="4">
-        <v>0.44697399999999998</v>
+        <v>0.42799900000000002</v>
       </c>
       <c r="I331" s="3">
         <f t="shared" si="5"/>
+        <v>-1.2079999999999869E-3</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A332" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F332" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G332" s="4">
+        <v>0.46855400000000003</v>
+      </c>
+      <c r="H332" s="4">
+        <v>0.46905000000000002</v>
+      </c>
+      <c r="I332" s="3">
+        <f t="shared" si="5"/>
+        <v>4.9599999999999644E-4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A333" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F333" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G333" s="4">
+        <v>0.405422</v>
+      </c>
+      <c r="H333" s="4">
+        <v>0.40539399999999998</v>
+      </c>
+      <c r="I333" s="3">
+        <f t="shared" si="5"/>
+        <v>-2.8000000000028002E-5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A334" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F334" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G334" s="4">
+        <v>0.42799900000000002</v>
+      </c>
+      <c r="H334" s="4">
+        <v>0.42893199999999998</v>
+      </c>
+      <c r="I334" s="3">
+        <f t="shared" si="5"/>
+        <v>9.3299999999996164E-4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A335" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F335" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G335" s="4">
+        <v>0.46855400000000003</v>
+      </c>
+      <c r="H335" s="4">
+        <v>0.474468</v>
+      </c>
+      <c r="I335" s="3">
+        <f t="shared" si="5"/>
+        <v>5.9139999999999748E-3</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A336" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F336" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G336" s="4">
+        <v>0.405422</v>
+      </c>
+      <c r="H336" s="4">
+        <v>0.41612700000000002</v>
+      </c>
+      <c r="I336" s="3">
+        <f t="shared" si="5"/>
+        <v>1.070500000000002E-2</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A337" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F337" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G337" s="4">
+        <v>0.42799900000000002</v>
+      </c>
+      <c r="H337" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="I337" s="3">
+        <f t="shared" si="5"/>
+        <v>1.649299999999998E-2</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A338" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F338" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G338" s="4">
+        <v>0.474468</v>
+      </c>
+      <c r="H338" s="4">
+        <v>0.46881499999999998</v>
+      </c>
+      <c r="I338" s="3">
+        <f t="shared" si="5"/>
+        <v>-5.6530000000000191E-3</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A339" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F339" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G339" s="4">
+        <v>0.41612700000000002</v>
+      </c>
+      <c r="H339" s="4">
+        <v>0.41482400000000003</v>
+      </c>
+      <c r="I339" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.3029999999999986E-3</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A340" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F340" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G340" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="H340" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="I340" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A341" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F341" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G341" s="4">
+        <v>0.474468</v>
+      </c>
+      <c r="H341" s="4">
+        <v>0.46905000000000002</v>
+      </c>
+      <c r="I341" s="3">
+        <f t="shared" si="5"/>
+        <v>-5.4179999999999784E-3</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A342" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G342" s="4">
+        <v>0.41612700000000002</v>
+      </c>
+      <c r="H342" s="4">
+        <v>0.40539399999999998</v>
+      </c>
+      <c r="I342" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.0733000000000048E-2</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A343" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F343" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G343" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="H343" s="4">
+        <v>0.42893199999999998</v>
+      </c>
+      <c r="I343" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.5560000000000018E-2</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A344" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F344" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G344" s="4">
+        <v>0.474468</v>
+      </c>
+      <c r="H344" s="4">
+        <v>0.47445599999999999</v>
+      </c>
+      <c r="I344" s="3">
+        <f t="shared" si="5"/>
+        <v>-1.2000000000012001E-5</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A345" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F345" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G345" s="4">
+        <v>0.41612700000000002</v>
+      </c>
+      <c r="H345" s="4">
+        <v>0.41566900000000001</v>
+      </c>
+      <c r="I345" s="3">
+        <f t="shared" si="5"/>
+        <v>-4.5800000000001395E-4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A346" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F346" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G346" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="H346" s="4">
+        <v>0.44368299999999999</v>
+      </c>
+      <c r="I346" s="3">
+        <f t="shared" si="5"/>
+        <v>-8.0900000000000416E-4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A347" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F347" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G347" s="4">
+        <v>0.474468</v>
+      </c>
+      <c r="H347" s="4">
+        <v>0.47425499999999998</v>
+      </c>
+      <c r="I347" s="3">
+        <f t="shared" si="5"/>
+        <v>-2.1300000000001873E-4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A348" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F348" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G348" s="4">
+        <v>0.41612700000000002</v>
+      </c>
+      <c r="H348" s="4">
+        <v>0.41640199999999999</v>
+      </c>
+      <c r="I348" s="3">
+        <f t="shared" si="5"/>
+        <v>2.7499999999996971E-4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A349" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F349" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G349" s="4">
+        <v>0.444492</v>
+      </c>
+      <c r="H349" s="4">
+        <v>0.44697399999999998</v>
+      </c>
+      <c r="I349" s="3">
+        <f t="shared" si="5"/>
         <v>2.4819999999999842E-3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I331" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:I349" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13262,7 +13945,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -13271,54 +13954,54 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
@@ -13327,26 +14010,26 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
@@ -13355,12 +14038,12 @@
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
@@ -13369,21 +14052,21 @@
         <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -13402,47 +14085,47 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="28" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
